--- a/Design-Files/Carrier-Board-v1.0/BOM/eSpark_BOM_Carrier-Board-v1.0.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/eSpark_BOM_Carrier-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="881">
   <si>
     <t>Component list</t>
   </si>
@@ -2544,9 +2544,6 @@
     <t>HJ-SMA175</t>
   </si>
   <si>
-    <t>MCZ1210CH900CPTA0G</t>
-  </si>
-  <si>
     <t>MAX3232EIDR</t>
   </si>
   <si>
@@ -2659,6 +2656,12 @@
   </si>
   <si>
     <t>R58, R66, R198</t>
+  </si>
+  <si>
+    <t>MCZ1210CH900L2TA0G</t>
+  </si>
+  <si>
+    <t>C307688</t>
   </si>
 </sst>
 </file>
@@ -3312,6 +3315,29 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3333,29 +3359,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3734,15 +3737,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="62"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3767,7 +3770,7 @@
       <c r="P2" s="33"/>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
-      <c r="S2" s="65"/>
+      <c r="S2" s="74"/>
     </row>
     <row r="3" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -3792,7 +3795,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
-      <c r="S3" s="66"/>
+      <c r="S3" s="75"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3813,7 +3816,7 @@
       <c r="P4" s="25"/>
       <c r="Q4" s="25"/>
       <c r="R4" s="25"/>
-      <c r="S4" s="66"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3834,7 +3837,7 @@
       <c r="P5" s="36"/>
       <c r="Q5" s="36"/>
       <c r="R5" s="36"/>
-      <c r="S5" s="66"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -3855,7 +3858,7 @@
       <c r="P6" s="36"/>
       <c r="Q6" s="36"/>
       <c r="R6" s="36"/>
-      <c r="S6" s="67"/>
+      <c r="S6" s="76"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -4163,10 +4166,10 @@
         <v>545</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K12" s="43" t="s">
         <v>746</v>
@@ -6885,13 +6888,13 @@
         <v>54</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D61" s="21" t="s">
         <v>95</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F61" s="21" t="s">
         <v>833</v>
@@ -6900,13 +6903,13 @@
         <v>840</v>
       </c>
       <c r="H61" s="21" t="s">
+        <v>844</v>
+      </c>
+      <c r="I61" s="21" t="s">
+        <v>811</v>
+      </c>
+      <c r="J61" s="21" t="s">
         <v>845</v>
-      </c>
-      <c r="I61" s="21" t="s">
-        <v>811</v>
-      </c>
-      <c r="J61" s="21" t="s">
-        <v>846</v>
       </c>
       <c r="K61" s="48" t="s">
         <v>811</v>
@@ -7725,19 +7728,19 @@
         <v>69</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D76" s="21" t="s">
         <v>110</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F76" s="21" t="s">
         <v>833</v>
       </c>
       <c r="G76" s="21" t="s">
-        <v>841</v>
+        <v>879</v>
       </c>
       <c r="H76" s="21" t="s">
         <v>547</v>
@@ -7746,7 +7749,7 @@
         <v>811</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>811</v>
+        <v>880</v>
       </c>
       <c r="K76" s="48" t="s">
         <v>811</v>
@@ -7761,11 +7764,15 @@
       <c r="N76" s="21">
         <v>15</v>
       </c>
-      <c r="O76" s="53"/>
-      <c r="P76" s="22"/>
+      <c r="O76" s="53" t="s">
+        <v>835</v>
+      </c>
+      <c r="P76" s="22">
+        <v>8.8599999999999998E-2</v>
+      </c>
       <c r="Q76" s="22">
         <f t="shared" ref="Q76" si="37">P76*N76</f>
-        <v>0</v>
+        <v>1.329</v>
       </c>
       <c r="R76" s="21"/>
       <c r="S76" s="21"/>
@@ -8131,10 +8138,10 @@
         <v>576</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="K83" s="43" t="s">
         <v>811</v>
@@ -8187,10 +8194,10 @@
         <v>576</v>
       </c>
       <c r="I84" s="21" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K84" s="43" t="s">
         <v>811</v>
@@ -8243,10 +8250,10 @@
         <v>576</v>
       </c>
       <c r="I85" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="J85" s="14" t="s">
         <v>861</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>862</v>
       </c>
       <c r="K85" s="43" t="s">
         <v>811</v>
@@ -9045,7 +9052,7 @@
       <c r="N99" s="45">
         <v>100</v>
       </c>
-      <c r="O99" s="68" t="s">
+      <c r="O99" s="61" t="s">
         <v>835</v>
       </c>
       <c r="P99" s="15" t="s">
@@ -9055,8 +9062,8 @@
         <v>811</v>
       </c>
       <c r="R99" s="45"/>
-      <c r="S99" s="69" t="s">
-        <v>868</v>
+      <c r="S99" s="62" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -9586,10 +9593,10 @@
         <v>545</v>
       </c>
       <c r="I109" s="14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K109" s="48" t="s">
         <v>779</v>
@@ -9772,7 +9779,7 @@
       <c r="N112" s="45">
         <v>100</v>
       </c>
-      <c r="O112" s="68" t="s">
+      <c r="O112" s="61" t="s">
         <v>835</v>
       </c>
       <c r="P112" s="15" t="s">
@@ -9782,8 +9789,8 @@
         <v>811</v>
       </c>
       <c r="R112" s="45"/>
-      <c r="S112" s="69" t="s">
-        <v>868</v>
+      <c r="S112" s="62" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
@@ -9796,7 +9803,7 @@
         <v>34</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>298</v>
@@ -9814,7 +9821,7 @@
         <v>811</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K113" s="48" t="s">
         <v>782</v>
@@ -9941,7 +9948,7 @@
       <c r="N115" s="45">
         <v>100</v>
       </c>
-      <c r="O115" s="68" t="s">
+      <c r="O115" s="61" t="s">
         <v>835</v>
       </c>
       <c r="P115" s="15" t="s">
@@ -9951,8 +9958,8 @@
         <v>811</v>
       </c>
       <c r="R115" s="45"/>
-      <c r="S115" s="69" t="s">
-        <v>868</v>
+      <c r="S115" s="62" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
@@ -10148,10 +10155,10 @@
         <v>583</v>
       </c>
       <c r="I119" s="21" t="s">
+        <v>876</v>
+      </c>
+      <c r="J119" s="14" t="s">
         <v>877</v>
-      </c>
-      <c r="J119" s="14" t="s">
-        <v>878</v>
       </c>
       <c r="K119" s="48" t="s">
         <v>785</v>
@@ -10558,7 +10565,7 @@
       <c r="N126" s="45">
         <v>100</v>
       </c>
-      <c r="O126" s="68" t="s">
+      <c r="O126" s="61" t="s">
         <v>835</v>
       </c>
       <c r="P126" s="15" t="s">
@@ -10568,8 +10575,8 @@
         <v>811</v>
       </c>
       <c r="R126" s="45"/>
-      <c r="S126" s="69" t="s">
-        <v>868</v>
+      <c r="S126" s="62" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
@@ -11045,10 +11052,10 @@
         <v>584</v>
       </c>
       <c r="I135" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="J135" s="21" t="s">
         <v>863</v>
-      </c>
-      <c r="J135" s="21" t="s">
-        <v>864</v>
       </c>
       <c r="K135" s="43" t="s">
         <v>772</v>
@@ -11201,13 +11208,13 @@
         <v>171</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F138" s="14" t="s">
         <v>400</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H138" s="14" t="s">
         <v>587</v>
@@ -11216,7 +11223,7 @@
         <v>811</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K138" s="48" t="s">
         <v>811</v>
@@ -11272,7 +11279,7 @@
         <v>811</v>
       </c>
       <c r="J139" s="21" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="K139" s="48" t="s">
         <v>811</v>
@@ -11328,7 +11335,7 @@
         <v>811</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K140" s="48" t="s">
         <v>811</v>
@@ -11568,7 +11575,7 @@
         <v>4</v>
       </c>
       <c r="O144" s="53" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="P144" s="15">
         <v>2.64</v>
@@ -11624,7 +11631,7 @@
         <v>4</v>
       </c>
       <c r="O145" s="53" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="P145" s="15">
         <v>2.91</v>
@@ -11680,7 +11687,7 @@
         <v>4</v>
       </c>
       <c r="O146" s="53" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="P146" s="15">
         <v>9.9945000000000004</v>
@@ -11720,7 +11727,7 @@
         <v>811</v>
       </c>
       <c r="J147" s="21" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K147" s="48" t="s">
         <v>811</v>
@@ -11832,7 +11839,7 @@
         <v>811</v>
       </c>
       <c r="J149" s="21" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K149" s="48" t="s">
         <v>811</v>
@@ -12000,7 +12007,7 @@
         <v>811</v>
       </c>
       <c r="J152" s="14" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K152" s="48" t="s">
         <v>811</v>
@@ -12184,7 +12191,7 @@
         <v>4</v>
       </c>
       <c r="O155" s="53" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="P155" s="22">
         <v>0.61199999999999999</v>
@@ -12700,26 +12707,26 @@
       <c r="R164" s="14"/>
       <c r="S164" s="20"/>
     </row>
-    <row r="165" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="70"/>
-      <c r="B165" s="71">
+    <row r="165" spans="1:19" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="63"/>
+      <c r="B165" s="64">
         <f t="shared" ref="B165:B171" si="80">ROW(B165) - ROW($B$7)</f>
         <v>158</v>
       </c>
-      <c r="C165" s="72" t="s">
+      <c r="C165" s="65" t="s">
         <v>813</v>
       </c>
       <c r="D165" s="46" t="s">
         <v>814</v>
       </c>
       <c r="E165" s="50" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F165" s="47" t="s">
         <v>833</v>
       </c>
       <c r="G165" s="50" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H165" s="46" t="s">
         <v>565</v>
@@ -12728,7 +12735,7 @@
         <v>811</v>
       </c>
       <c r="J165" s="46" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K165" s="50" t="s">
         <v>811</v>
@@ -12743,10 +12750,10 @@
       <c r="N165" s="46">
         <v>4</v>
       </c>
-      <c r="O165" s="73" t="s">
-        <v>835</v>
-      </c>
-      <c r="P165" s="74">
+      <c r="O165" s="66" t="s">
+        <v>835</v>
+      </c>
+      <c r="P165" s="67">
         <v>1.0093000000000001</v>
       </c>
       <c r="Q165" s="15">
@@ -12756,20 +12763,20 @@
       <c r="R165" s="46"/>
       <c r="S165" s="20"/>
     </row>
-    <row r="166" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="70"/>
-      <c r="B166" s="71">
+    <row r="166" spans="1:19" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="63"/>
+      <c r="B166" s="64">
         <f t="shared" si="80"/>
         <v>159</v>
       </c>
-      <c r="C166" s="72" t="s">
+      <c r="C166" s="65" t="s">
         <v>813</v>
       </c>
       <c r="D166" s="46" t="s">
         <v>815</v>
       </c>
       <c r="E166" s="50" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F166" s="47" t="s">
         <v>811</v>
@@ -12784,7 +12791,7 @@
         <v>811</v>
       </c>
       <c r="J166" s="46" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K166" s="50" t="s">
         <v>811</v>
@@ -12799,10 +12806,10 @@
       <c r="N166" s="46">
         <v>4</v>
       </c>
-      <c r="O166" s="76" t="s">
-        <v>835</v>
-      </c>
-      <c r="P166" s="74">
+      <c r="O166" s="69" t="s">
+        <v>835</v>
+      </c>
+      <c r="P166" s="67">
         <v>0.42520000000000002</v>
       </c>
       <c r="Q166" s="15">
@@ -13078,14 +13085,14 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
-      <c r="N172" s="63" t="s">
+      <c r="N172" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="O172" s="64"/>
-      <c r="P172" s="64"/>
+      <c r="O172" s="73"/>
+      <c r="P172" s="73"/>
       <c r="Q172" s="18">
         <f>SUM(Q8:Q171)</f>
-        <v>640.41830000000027</v>
+        <v>641.74730000000022</v>
       </c>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
@@ -13104,14 +13111,14 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
-      <c r="N173" s="63" t="s">
+      <c r="N173" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="O173" s="64"/>
-      <c r="P173" s="64"/>
+      <c r="O173" s="73"/>
+      <c r="P173" s="73"/>
       <c r="Q173" s="19">
         <f>Q172/3</f>
-        <v>213.47276666666676</v>
+        <v>213.91576666666674</v>
       </c>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
@@ -13286,9 +13293,10 @@
     <hyperlink ref="O113" r:id="rId157"/>
     <hyperlink ref="O165" r:id="rId158"/>
     <hyperlink ref="O119" r:id="rId159"/>
+    <hyperlink ref="O76" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId160"/>
-  <drawing r:id="rId161"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId161"/>
+  <drawing r:id="rId162"/>
 </worksheet>
 </file>
--- a/Design-Files/Carrier-Board-v1.0/BOM/eSpark_BOM_Carrier-Board-v1.0.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/eSpark_BOM_Carrier-Board-v1.0.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20409"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\anis-carrierboard\Design-Files\Carrier-Board-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eSpark Cons Group\Documents\GitHub\Melih-SoundSensor\anis-carrierboard\Design-Files\Carrier-Board-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE24D97-08CA-4F89-9C65-C43B7CFEFB79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="877">
   <si>
     <t>Component list</t>
   </si>
@@ -678,9 +679,6 @@
     <t>CAP CER 10UF 10V X5R 0402</t>
   </si>
   <si>
-    <t>CAP CER 9PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
     <t>CAP CER 10UF 25V X5R 0603</t>
   </si>
   <si>
@@ -1350,9 +1348,6 @@
     <t>CC0402MRX5R6BB106</t>
   </si>
   <si>
-    <t>CQ0402CRNPO9BN9R0</t>
-  </si>
-  <si>
     <t>C1608X5R1E106M080AC</t>
   </si>
   <si>
@@ -1905,9 +1900,6 @@
     <t>C962143</t>
   </si>
   <si>
-    <t>C577403</t>
-  </si>
-  <si>
     <t>C2168289</t>
   </si>
   <si>
@@ -2290,9 +2282,6 @@
   </si>
   <si>
     <t>220nF</t>
-  </si>
-  <si>
-    <t>9pF</t>
   </si>
   <si>
     <t>4.7uF</t>
@@ -2667,7 +2656,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -3153,7 +3142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3360,6 +3349,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3701,7 +3693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S185"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3756,7 +3748,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="41" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -3781,7 +3773,7 @@
       </c>
       <c r="E3" s="28"/>
       <c r="F3" s="42" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="G3" s="30"/>
       <c r="H3" s="31"/>
@@ -3875,46 +3867,46 @@
         <v>198</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="P7" s="59" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="R7" s="12" t="s">
         <v>802</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>608</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="S7" s="12" t="s">
         <v>803</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>799</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>804</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>808</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>805</v>
-      </c>
-      <c r="P7" s="59" t="s">
-        <v>809</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>810</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>806</v>
-      </c>
-      <c r="S7" s="12" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="180" x14ac:dyDescent="0.25">
@@ -3933,22 +3925,22 @@
         <v>199</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="L8" s="14">
         <v>97</v>
@@ -3961,7 +3953,7 @@
         <v>300</v>
       </c>
       <c r="O8" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P8" s="60">
         <v>1E-3</v>
@@ -3989,22 +3981,22 @@
         <v>200</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K9" s="48" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="L9" s="21">
         <v>2</v>
@@ -4017,7 +4009,7 @@
         <v>100</v>
       </c>
       <c r="O9" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P9" s="60">
         <v>1E-3</v>
@@ -4045,22 +4037,22 @@
         <v>201</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="L10" s="14">
         <v>7</v>
@@ -4073,7 +4065,7 @@
         <v>50</v>
       </c>
       <c r="O10" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P10" s="60">
         <v>1.1299999999999999E-2</v>
@@ -4101,22 +4093,22 @@
         <v>202</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="K11" s="48" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="L11" s="21">
         <v>4</v>
@@ -4129,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P11" s="60">
         <v>3.8E-3</v>
@@ -4157,22 +4149,22 @@
         <v>203</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G12" s="45" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L12" s="14">
         <v>4</v>
@@ -4185,7 +4177,7 @@
         <v>50</v>
       </c>
       <c r="O12" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P12" s="60">
         <v>1.2500000000000001E-2</v>
@@ -4213,22 +4205,22 @@
         <v>204</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="K13" s="48" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="L13" s="21">
         <v>3</v>
@@ -4241,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="O13" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P13" s="60">
         <v>3.78E-2</v>
@@ -4269,22 +4261,22 @@
         <v>205</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="L14" s="14">
         <v>4</v>
@@ -4297,7 +4289,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P14" s="60">
         <v>7.0000000000000001E-3</v>
@@ -4325,22 +4317,22 @@
         <v>206</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="L15" s="21">
         <v>13</v>
@@ -4353,7 +4345,7 @@
         <v>50</v>
       </c>
       <c r="O15" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P15" s="60">
         <v>1.2500000000000001E-2</v>
@@ -4381,22 +4373,22 @@
         <v>207</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L16" s="14">
         <v>4</v>
@@ -4409,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="O16" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P16" s="60">
         <v>0.1429</v>
@@ -4437,22 +4429,22 @@
         <v>208</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="K17" s="48" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="L17" s="21">
         <v>4</v>
@@ -4465,7 +4457,7 @@
         <v>15</v>
       </c>
       <c r="O17" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P17" s="60">
         <v>0.28210000000000002</v>
@@ -4493,22 +4485,22 @@
         <v>209</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="L18" s="14">
         <v>2</v>
@@ -4521,7 +4513,7 @@
         <v>50</v>
       </c>
       <c r="O18" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P18" s="60">
         <v>1.5100000000000001E-2</v>
@@ -4549,22 +4541,22 @@
         <v>210</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="K19" s="48" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="L19" s="21">
         <v>2</v>
@@ -4577,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P19" s="60">
         <v>1.1000000000000001E-3</v>
@@ -4605,22 +4597,22 @@
         <v>211</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="L20" s="14">
         <v>2</v>
@@ -4633,7 +4625,7 @@
         <v>100</v>
       </c>
       <c r="O20" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P20" s="60">
         <v>2.3999999999999998E-3</v>
@@ -4661,22 +4653,22 @@
         <v>212</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="K21" s="48" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="L21" s="21">
         <v>2</v>
@@ -4689,7 +4681,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P21" s="60">
         <v>2E-3</v>
@@ -4717,22 +4709,22 @@
         <v>213</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="K22" s="43" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="L22" s="14">
         <v>1</v>
@@ -4745,7 +4737,7 @@
         <v>4</v>
       </c>
       <c r="O22" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P22" s="60">
         <v>0.89149999999999996</v>
@@ -4773,22 +4765,22 @@
         <v>214</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="K23" s="48" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="L23" s="21">
         <v>1</v>
@@ -4801,7 +4793,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P23" s="60">
         <v>3.2000000000000002E-3</v>
@@ -4829,22 +4821,22 @@
         <v>215</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="K24" s="43" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -4857,7 +4849,7 @@
         <v>20</v>
       </c>
       <c r="O24" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P24" s="60">
         <v>2.3E-2</v>
@@ -4885,22 +4877,22 @@
         <v>216</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J25" s="21" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="K25" s="48" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="L25" s="21">
         <v>2</v>
@@ -4913,7 +4905,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P25" s="60">
         <v>0.20760000000000001</v>
@@ -4941,22 +4933,22 @@
         <v>217</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="K26" s="43" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="L26" s="14">
         <v>2</v>
@@ -4969,7 +4961,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P26" s="60">
         <v>5.7000000000000002E-3</v>
@@ -4997,22 +4989,22 @@
         <v>218</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="K27" s="48" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L27" s="21">
         <v>1</v>
@@ -5025,7 +5017,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P27" s="60">
         <v>2.3099999999999999E-2</v>
@@ -5050,25 +5042,25 @@
         <v>62</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K28" s="43" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L28" s="14">
         <v>2</v>
@@ -5080,15 +5072,15 @@
       <c r="N28" s="14">
         <v>50</v>
       </c>
-      <c r="O28" s="56" t="s">
-        <v>835</v>
+      <c r="O28" s="77" t="s">
+        <v>831</v>
       </c>
       <c r="P28" s="60">
-        <v>7.7000000000000002E-3</v>
+        <v>4.5900000000000003E-2</v>
       </c>
       <c r="Q28" s="57">
         <f>P28*N28</f>
-        <v>0.38500000000000001</v>
+        <v>2.2950000000000004</v>
       </c>
       <c r="R28" s="14"/>
       <c r="S28" s="20"/>
@@ -5106,25 +5098,25 @@
         <v>63</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J29" s="21" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="K29" s="48" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L29" s="21">
         <v>10</v>
@@ -5137,7 +5129,7 @@
         <v>32</v>
       </c>
       <c r="O29" s="56" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P29" s="60">
         <v>0.3357</v>
@@ -5162,25 +5154,25 @@
         <v>64</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="L30" s="14">
         <v>1</v>
@@ -5193,7 +5185,7 @@
         <v>10</v>
       </c>
       <c r="O30" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P30" s="15">
         <v>5.6800000000000003E-2</v>
@@ -5218,25 +5210,25 @@
         <v>65</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J31" s="21" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="K31" s="48" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="L31" s="21">
         <v>7</v>
@@ -5249,7 +5241,7 @@
         <v>50</v>
       </c>
       <c r="O31" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P31" s="15">
         <v>1.67E-2</v>
@@ -5274,25 +5266,25 @@
         <v>66</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="K32" s="43" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="L32" s="14">
         <v>4</v>
@@ -5305,7 +5297,7 @@
         <v>20</v>
       </c>
       <c r="O32" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P32" s="15">
         <v>4.5900000000000003E-2</v>
@@ -5333,22 +5325,22 @@
         <v>210</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J33" s="21" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="K33" s="48" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="L33" s="21">
         <v>7</v>
@@ -5361,7 +5353,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P33" s="15">
         <v>1.1000000000000001E-3</v>
@@ -5386,25 +5378,25 @@
         <v>68</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="K34" s="43" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="L34" s="14">
         <v>2</v>
@@ -5417,7 +5409,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P34" s="15">
         <v>1.4E-3</v>
@@ -5442,25 +5434,25 @@
         <v>69</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J35" s="21" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="L35" s="21">
         <v>2</v>
@@ -5473,7 +5465,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P35" s="15">
         <v>2.3E-3</v>
@@ -5498,25 +5490,25 @@
         <v>70</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="K36" s="43" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="L36" s="14">
         <v>1</v>
@@ -5529,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="O36" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P36" s="15">
         <v>4.7000000000000002E-3</v>
@@ -5554,25 +5546,25 @@
         <v>71</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="L37" s="21">
         <v>2</v>
@@ -5585,7 +5577,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P37" s="15">
         <v>3.8999999999999998E-3</v>
@@ -5610,25 +5602,25 @@
         <v>72</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="K38" s="43" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="L38" s="14">
         <v>1</v>
@@ -5641,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="O38" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P38" s="15">
         <v>5.1000000000000004E-3</v>
@@ -5666,25 +5658,25 @@
         <v>73</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L39" s="21">
         <v>30</v>
@@ -5697,7 +5689,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P39" s="15">
         <v>8.3000000000000001E-3</v>
@@ -5722,25 +5714,25 @@
         <v>74</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="K40" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L40" s="14">
         <v>2</v>
@@ -5753,7 +5745,7 @@
         <v>10</v>
       </c>
       <c r="O40" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P40" s="15">
         <v>6.2600000000000003E-2</v>
@@ -5778,25 +5770,25 @@
         <v>75</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J41" s="21" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L41" s="21">
         <v>1</v>
@@ -5809,7 +5801,7 @@
         <v>5</v>
       </c>
       <c r="O41" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P41" s="15">
         <v>9.9299999999999999E-2</v>
@@ -5834,25 +5826,25 @@
         <v>76</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="K42" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L42" s="14">
         <v>6</v>
@@ -5865,7 +5857,7 @@
         <v>20</v>
       </c>
       <c r="O42" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P42" s="15">
         <v>0.12529999999999999</v>
@@ -5890,25 +5882,25 @@
         <v>77</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J43" s="21" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="K43" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L43" s="21">
         <v>1</v>
@@ -5921,7 +5913,7 @@
         <v>10</v>
       </c>
       <c r="O43" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P43" s="15">
         <v>4.6300000000000001E-2</v>
@@ -5946,25 +5938,25 @@
         <v>78</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="K44" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L44" s="14">
         <v>21</v>
@@ -5977,7 +5969,7 @@
         <v>80</v>
       </c>
       <c r="O44" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P44" s="15">
         <v>1.9099999999999999E-2</v>
@@ -6002,25 +5994,25 @@
         <v>79</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J45" s="21" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="K45" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L45" s="21">
         <v>1</v>
@@ -6033,7 +6025,7 @@
         <v>10</v>
       </c>
       <c r="O45" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P45" s="15">
         <v>7.9399999999999998E-2</v>
@@ -6058,25 +6050,25 @@
         <v>80</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="K46" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L46" s="14">
         <v>2</v>
@@ -6089,7 +6081,7 @@
         <v>20</v>
       </c>
       <c r="O46" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P46" s="15">
         <v>2.9100000000000001E-2</v>
@@ -6114,25 +6106,25 @@
         <v>81</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J47" s="21" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K47" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L47" s="21">
         <v>2</v>
@@ -6145,7 +6137,7 @@
         <v>10</v>
       </c>
       <c r="O47" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P47" s="15">
         <v>8.0699999999999994E-2</v>
@@ -6170,25 +6162,25 @@
         <v>82</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="K48" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L48" s="14">
         <v>1</v>
@@ -6201,7 +6193,7 @@
         <v>4</v>
       </c>
       <c r="O48" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P48" s="15">
         <v>0.378</v>
@@ -6226,25 +6218,25 @@
         <v>83</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="K49" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L49" s="21">
         <v>1</v>
@@ -6257,7 +6249,7 @@
         <v>10</v>
       </c>
       <c r="O49" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P49" s="15">
         <v>3.9399999999999998E-2</v>
@@ -6282,21 +6274,21 @@
         <v>84</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="K50" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L50" s="14">
         <v>1</v>
@@ -6309,7 +6301,7 @@
         <v>50</v>
       </c>
       <c r="O50" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P50" s="15">
         <v>1.7600000000000001E-2</v>
@@ -6334,25 +6326,25 @@
         <v>85</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J51" s="21" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="K51" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L51" s="21">
         <v>1</v>
@@ -6365,7 +6357,7 @@
         <v>100</v>
       </c>
       <c r="O51" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P51" s="15">
         <v>6.4000000000000003E-3</v>
@@ -6390,25 +6382,25 @@
         <v>86</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="K52" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L52" s="14">
         <v>2</v>
@@ -6421,7 +6413,7 @@
         <v>10</v>
       </c>
       <c r="O52" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P52" s="15">
         <v>0.15340000000000001</v>
@@ -6446,25 +6438,25 @@
         <v>87</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="K53" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L53" s="21">
         <v>1</v>
@@ -6477,7 +6469,7 @@
         <v>5</v>
       </c>
       <c r="O53" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P53" s="15">
         <v>7.4099999999999999E-2</v>
@@ -6502,25 +6494,25 @@
         <v>88</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="K54" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -6533,7 +6525,7 @@
         <v>4</v>
       </c>
       <c r="O54" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P54" s="15">
         <v>4.0294999999999996</v>
@@ -6558,25 +6550,25 @@
         <v>89</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J55" s="21" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="K55" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L55" s="21">
         <v>1</v>
@@ -6589,7 +6581,7 @@
         <v>4</v>
       </c>
       <c r="O55" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P55" s="15">
         <v>0.55059999999999998</v>
@@ -6614,25 +6606,25 @@
         <v>90</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K56" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L56" s="14">
         <v>1</v>
@@ -6645,7 +6637,7 @@
         <v>50</v>
       </c>
       <c r="O56" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P56" s="15">
         <v>1.52E-2</v>
@@ -6670,25 +6662,25 @@
         <v>91</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H57" s="21" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J57" s="21" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="K57" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L57" s="21">
         <v>1</v>
@@ -6701,7 +6693,7 @@
         <v>20</v>
       </c>
       <c r="O57" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P57" s="15">
         <v>1.9199999999999998E-2</v>
@@ -6726,25 +6718,25 @@
         <v>92</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K58" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L58" s="14">
         <v>1</v>
@@ -6757,7 +6749,7 @@
         <v>5</v>
       </c>
       <c r="O58" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P58" s="15">
         <v>0.1726</v>
@@ -6782,25 +6774,25 @@
         <v>93</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="K59" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L59" s="21">
         <v>1</v>
@@ -6813,7 +6805,7 @@
         <v>4</v>
       </c>
       <c r="O59" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P59" s="15">
         <v>0.70579999999999998</v>
@@ -6838,25 +6830,25 @@
         <v>94</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="K60" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L60" s="14">
         <v>1</v>
@@ -6869,7 +6861,7 @@
         <v>4</v>
       </c>
       <c r="O60" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P60" s="15">
         <v>0.42970000000000003</v>
@@ -6888,31 +6880,31 @@
         <v>54</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D61" s="21" t="s">
         <v>95</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G61" s="21" t="s">
+        <v>836</v>
+      </c>
+      <c r="H61" s="21" t="s">
         <v>840</v>
       </c>
-      <c r="H61" s="21" t="s">
-        <v>844</v>
-      </c>
       <c r="I61" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="K61" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L61" s="21">
         <v>1</v>
@@ -6925,7 +6917,7 @@
         <v>4</v>
       </c>
       <c r="O61" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P61" s="15">
         <v>0.80400000000000005</v>
@@ -6950,25 +6942,25 @@
         <v>96</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J62" s="21" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="K62" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L62" s="21">
         <v>2</v>
@@ -6981,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="O62" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P62" s="15">
         <v>0.55000000000000004</v>
@@ -7006,25 +6998,25 @@
         <v>97</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="K63" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L63" s="14">
         <v>5</v>
@@ -7037,7 +7029,7 @@
         <v>20</v>
       </c>
       <c r="O63" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P63" s="15">
         <v>9.8699999999999996E-2</v>
@@ -7062,25 +7054,25 @@
         <v>98</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G64" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H64" s="21" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J64" s="21" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="K64" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L64" s="21">
         <v>1</v>
@@ -7093,7 +7085,7 @@
         <v>5</v>
       </c>
       <c r="O64" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P64" s="15">
         <v>0.18920000000000001</v>
@@ -7118,25 +7110,25 @@
         <v>99</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="K65" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L65" s="14">
         <v>1</v>
@@ -7149,7 +7141,7 @@
         <v>5</v>
       </c>
       <c r="O65" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P65" s="15">
         <v>7.6700000000000004E-2</v>
@@ -7174,25 +7166,25 @@
         <v>100</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G66" s="21" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="K66" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L66" s="21">
         <v>1</v>
@@ -7205,7 +7197,7 @@
         <v>5</v>
       </c>
       <c r="O66" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P66" s="22">
         <v>0.2258</v>
@@ -7230,25 +7222,25 @@
         <v>101</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L67" s="14">
         <v>1</v>
@@ -7261,7 +7253,7 @@
         <v>50</v>
       </c>
       <c r="O67" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P67" s="15">
         <v>1.2999999999999999E-2</v>
@@ -7286,25 +7278,25 @@
         <v>102</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G68" s="21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H68" s="21" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="K68" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L68" s="21">
         <v>2</v>
@@ -7317,7 +7309,7 @@
         <v>7</v>
       </c>
       <c r="O68" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P68" s="22">
         <v>2.5537999999999998</v>
@@ -7342,25 +7334,25 @@
         <v>103</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H69" s="14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="K69" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L69" s="14">
         <v>1</v>
@@ -7373,7 +7365,7 @@
         <v>50</v>
       </c>
       <c r="O69" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P69" s="15">
         <v>1.4999999999999999E-2</v>
@@ -7398,25 +7390,25 @@
         <v>104</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G70" s="21" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I70" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J70" s="21" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="K70" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L70" s="21">
         <v>1</v>
@@ -7429,7 +7421,7 @@
         <v>20</v>
       </c>
       <c r="O70" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P70" s="22">
         <v>1.67E-2</v>
@@ -7454,25 +7446,25 @@
         <v>105</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H71" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="K71" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L71" s="14">
         <v>1</v>
@@ -7485,7 +7477,7 @@
         <v>4</v>
       </c>
       <c r="O71" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P71" s="15">
         <v>0.33900000000000002</v>
@@ -7510,25 +7502,25 @@
         <v>106</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G72" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H72" s="21" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I72" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J72" s="21" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="K72" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L72" s="21">
         <v>1</v>
@@ -7541,7 +7533,7 @@
         <v>5</v>
       </c>
       <c r="O72" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P72" s="22">
         <v>0.27039999999999997</v>
@@ -7566,25 +7558,25 @@
         <v>107</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H73" s="14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I73" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="K73" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L73" s="14">
         <v>2</v>
@@ -7597,7 +7589,7 @@
         <v>100</v>
       </c>
       <c r="O73" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P73" s="15">
         <v>6.8999999999999999E-3</v>
@@ -7622,25 +7614,25 @@
         <v>108</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G74" s="21" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H74" s="21" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I74" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J74" s="21" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="K74" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L74" s="21">
         <v>1</v>
@@ -7653,7 +7645,7 @@
         <v>4</v>
       </c>
       <c r="O74" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P74" s="22">
         <v>0.49419999999999997</v>
@@ -7678,25 +7670,25 @@
         <v>109</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H75" s="14" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="K75" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L75" s="14">
         <v>5</v>
@@ -7709,7 +7701,7 @@
         <v>16</v>
       </c>
       <c r="O75" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P75" s="15">
         <v>0.72409999999999997</v>
@@ -7728,31 +7720,31 @@
         <v>69</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D76" s="21" t="s">
         <v>110</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G76" s="21" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="H76" s="21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I76" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J76" s="21" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="K76" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L76" s="21">
         <v>4</v>
@@ -7765,7 +7757,7 @@
         <v>15</v>
       </c>
       <c r="O76" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P76" s="22">
         <v>8.8599999999999998E-2</v>
@@ -7790,25 +7782,25 @@
         <v>111</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H77" s="14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I77" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="K77" s="48" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="L77" s="14">
         <v>1</v>
@@ -7821,7 +7813,7 @@
         <v>10</v>
       </c>
       <c r="O77" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P77" s="15">
         <v>4.6399999999999997E-2</v>
@@ -7846,25 +7838,25 @@
         <v>112</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G78" s="21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="I78" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J78" s="21" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="K78" s="43" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="L78" s="21">
         <v>2</v>
@@ -7877,7 +7869,7 @@
         <v>10</v>
       </c>
       <c r="O78" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P78" s="22">
         <v>6.7699999999999996E-2</v>
@@ -7902,25 +7894,25 @@
         <v>113</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H79" s="14" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I79" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K79" s="48" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="L79" s="14">
         <v>2</v>
@@ -7933,7 +7925,7 @@
         <v>7</v>
       </c>
       <c r="O79" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P79" s="15">
         <v>0.79559999999999997</v>
@@ -7958,25 +7950,25 @@
         <v>114</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G80" s="21" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H80" s="21" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I80" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J80" s="21" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="K80" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L80" s="21">
         <v>1</v>
@@ -7989,7 +7981,7 @@
         <v>20</v>
       </c>
       <c r="O80" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P80" s="22">
         <v>2.18E-2</v>
@@ -8014,25 +8006,25 @@
         <v>115</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G81" s="14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H81" s="14" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I81" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="K81" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L81" s="14">
         <v>2</v>
@@ -8045,7 +8037,7 @@
         <v>20</v>
       </c>
       <c r="O81" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P81" s="15">
         <v>2.18E-2</v>
@@ -8070,25 +8062,25 @@
         <v>116</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G82" s="21" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I82" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J82" s="21" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="K82" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L82" s="21">
         <v>1</v>
@@ -8101,7 +8093,7 @@
         <v>20</v>
       </c>
       <c r="O82" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P82" s="22">
         <v>1.9599999999999999E-2</v>
@@ -8126,25 +8118,25 @@
         <v>117</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G83" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H83" s="14" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="K83" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L83" s="14">
         <v>1</v>
@@ -8157,7 +8149,7 @@
         <v>50</v>
       </c>
       <c r="O83" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P83" s="15">
         <v>1.18E-2</v>
@@ -8182,25 +8174,25 @@
         <v>118</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G84" s="45" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H84" s="21" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I84" s="21" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="J84" s="21" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="K84" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L84" s="21">
         <v>1</v>
@@ -8213,7 +8205,7 @@
         <v>100</v>
       </c>
       <c r="O84" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P84" s="22">
         <v>6.1000000000000004E-3</v>
@@ -8238,25 +8230,25 @@
         <v>119</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G85" s="45" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H85" s="14" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="K85" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L85" s="14">
         <v>1</v>
@@ -8269,7 +8261,7 @@
         <v>50</v>
       </c>
       <c r="O85" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P85" s="15">
         <v>1.6E-2</v>
@@ -8294,25 +8286,25 @@
         <v>120</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G86" s="21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H86" s="21" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I86" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J86" s="21" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="K86" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L86" s="21">
         <v>6</v>
@@ -8325,7 +8317,7 @@
         <v>20</v>
       </c>
       <c r="O86" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P86" s="22">
         <v>7.7600000000000002E-2</v>
@@ -8350,25 +8342,25 @@
         <v>121</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G87" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H87" s="14" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="I87" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="K87" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L87" s="14">
         <v>1</v>
@@ -8381,7 +8373,7 @@
         <v>4</v>
       </c>
       <c r="O87" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P87" s="15">
         <v>0.437</v>
@@ -8406,25 +8398,25 @@
         <v>122</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G88" s="21" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H88" s="21" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I88" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J88" s="21" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="K88" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L88" s="21">
         <v>4</v>
@@ -8437,7 +8429,7 @@
         <v>15</v>
       </c>
       <c r="O88" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P88" s="22">
         <v>6.6900000000000001E-2</v>
@@ -8462,25 +8454,25 @@
         <v>123</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H89" s="14" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="I89" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="K89" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L89" s="14">
         <v>2</v>
@@ -8493,7 +8485,7 @@
         <v>50</v>
       </c>
       <c r="O89" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P89" s="15">
         <v>1.3599999999999999E-2</v>
@@ -8518,25 +8510,25 @@
         <v>124</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G90" s="21" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H90" s="21" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="I90" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J90" s="21" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K90" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L90" s="21">
         <v>5</v>
@@ -8549,7 +8541,7 @@
         <v>50</v>
       </c>
       <c r="O90" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P90" s="15">
         <v>9.9000000000000008E-3</v>
@@ -8574,25 +8566,25 @@
         <v>125</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="K91" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L91" s="14">
         <v>1</v>
@@ -8605,7 +8597,7 @@
         <v>5</v>
       </c>
       <c r="O91" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P91" s="15">
         <v>0.123</v>
@@ -8630,25 +8622,25 @@
         <v>126</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G92" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H92" s="21" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="I92" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J92" s="21" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="K92" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L92" s="21">
         <v>1</v>
@@ -8661,7 +8653,7 @@
         <v>20</v>
       </c>
       <c r="O92" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P92" s="15">
         <v>2.3300000000000001E-2</v>
@@ -8686,25 +8678,25 @@
         <v>127</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I93" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="K93" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L93" s="14">
         <v>1</v>
@@ -8717,7 +8709,7 @@
         <v>20</v>
       </c>
       <c r="O93" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P93" s="15">
         <v>2.8000000000000001E-2</v>
@@ -8742,25 +8734,25 @@
         <v>128</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G94" s="21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H94" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I94" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J94" s="21" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="K94" s="43" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="L94" s="21">
         <v>40</v>
@@ -8773,7 +8765,7 @@
         <v>100</v>
       </c>
       <c r="O94" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P94" s="15">
         <v>5.0000000000000001E-4</v>
@@ -8798,25 +8790,25 @@
         <v>129</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H95" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="K95" s="48" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="L95" s="14">
         <v>6</v>
@@ -8829,7 +8821,7 @@
         <v>100</v>
       </c>
       <c r="O95" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P95" s="15">
         <v>5.0000000000000001E-4</v>
@@ -8854,25 +8846,25 @@
         <v>130</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G96" s="21" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H96" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J96" s="21" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="K96" s="43" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="L96" s="21">
         <v>7</v>
@@ -8885,7 +8877,7 @@
         <v>100</v>
       </c>
       <c r="O96" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P96" s="15">
         <v>2.5999999999999999E-3</v>
@@ -8910,25 +8902,25 @@
         <v>131</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H97" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="K97" s="48" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="L97" s="14">
         <v>49</v>
@@ -8941,7 +8933,7 @@
         <v>200</v>
       </c>
       <c r="O97" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P97" s="15">
         <v>5.9999999999999995E-4</v>
@@ -8966,25 +8958,25 @@
         <v>132</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H98" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J98" s="21" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K98" s="43" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="L98" s="21">
         <v>7</v>
@@ -8997,7 +8989,7 @@
         <v>100</v>
       </c>
       <c r="O98" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P98" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9022,25 +9014,25 @@
         <v>133</v>
       </c>
       <c r="E99" s="45" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F99" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G99" s="45" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H99" s="45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J99" s="45" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="K99" s="49" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="L99" s="45">
         <v>2</v>
@@ -9053,17 +9045,17 @@
         <v>100</v>
       </c>
       <c r="O99" s="61" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P99" s="15" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="Q99" s="54" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="R99" s="45"/>
       <c r="S99" s="62" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -9079,25 +9071,25 @@
         <v>134</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H100" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J100" s="21" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="K100" s="43" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="L100" s="21">
         <v>2</v>
@@ -9110,7 +9102,7 @@
         <v>100</v>
       </c>
       <c r="O100" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P100" s="15">
         <v>1E-3</v>
@@ -9135,25 +9127,25 @@
         <v>135</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F101" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G101" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H101" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="K101" s="48" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="L101" s="14">
         <v>26</v>
@@ -9166,7 +9158,7 @@
         <v>100</v>
       </c>
       <c r="O101" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P101" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9191,25 +9183,25 @@
         <v>136</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G102" s="21" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H102" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I102" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J102" s="21" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="K102" s="43" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="L102" s="21">
         <v>1</v>
@@ -9222,7 +9214,7 @@
         <v>5</v>
       </c>
       <c r="O102" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P102" s="15">
         <v>0.13500000000000001</v>
@@ -9245,25 +9237,25 @@
         <v>137</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F103" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G103" s="14" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H103" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I103" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="K103" s="48" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="L103" s="14">
         <v>27</v>
@@ -9276,7 +9268,7 @@
         <v>100</v>
       </c>
       <c r="O103" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P103" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9301,25 +9293,25 @@
         <v>138</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G104" s="21" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H104" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I104" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J104" s="21" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="K104" s="43" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="L104" s="21">
         <v>4</v>
@@ -9332,7 +9324,7 @@
         <v>50</v>
       </c>
       <c r="O104" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P104" s="15">
         <v>8.3999999999999995E-3</v>
@@ -9357,25 +9349,25 @@
         <v>139</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G105" s="14" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H105" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I105" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="K105" s="48" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="L105" s="14">
         <v>4</v>
@@ -9388,7 +9380,7 @@
         <v>100</v>
       </c>
       <c r="O105" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P105" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9413,25 +9405,25 @@
         <v>140</v>
       </c>
       <c r="E106" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G106" s="21" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H106" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I106" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J106" s="21" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="K106" s="43" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L106" s="21">
         <v>4</v>
@@ -9444,7 +9436,7 @@
         <v>50</v>
       </c>
       <c r="O106" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P106" s="15">
         <v>9.7999999999999997E-3</v>
@@ -9469,25 +9461,25 @@
         <v>141</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F107" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G107" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H107" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I107" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="K107" s="48" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="L107" s="14">
         <v>1</v>
@@ -9500,7 +9492,7 @@
         <v>100</v>
       </c>
       <c r="O107" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P107" s="15">
         <v>1.1999999999999999E-3</v>
@@ -9525,25 +9517,25 @@
         <v>142</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G108" s="21" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H108" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I108" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="K108" s="43" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="L108" s="21">
         <v>5</v>
@@ -9556,7 +9548,7 @@
         <v>100</v>
       </c>
       <c r="O108" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P108" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9581,25 +9573,25 @@
         <v>143</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G109" s="45" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H109" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I109" s="14" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="K109" s="48" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="L109" s="14">
         <v>1</v>
@@ -9612,7 +9604,7 @@
         <v>100</v>
       </c>
       <c r="O109" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P109" s="15">
         <v>8.9999999999999998E-4</v>
@@ -9637,25 +9629,25 @@
         <v>144</v>
       </c>
       <c r="E110" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G110" s="21" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H110" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I110" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J110" s="21" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="K110" s="43" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="L110" s="21">
         <v>1</v>
@@ -9668,7 +9660,7 @@
         <v>100</v>
       </c>
       <c r="O110" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P110" s="15">
         <v>1.1999999999999999E-3</v>
@@ -9693,25 +9685,25 @@
         <v>145</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G111" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H111" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I111" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="K111" s="48" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="L111" s="14">
         <v>1</v>
@@ -9724,7 +9716,7 @@
         <v>100</v>
       </c>
       <c r="O111" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P111" s="15">
         <v>1E-3</v>
@@ -9749,25 +9741,25 @@
         <v>146</v>
       </c>
       <c r="E112" s="45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F112" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G112" s="45" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H112" s="45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I112" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J112" s="45" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="K112" s="49" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="L112" s="45">
         <v>1</v>
@@ -9780,17 +9772,17 @@
         <v>100</v>
       </c>
       <c r="O112" s="61" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P112" s="15" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="Q112" s="54" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="R112" s="45"/>
       <c r="S112" s="62" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
@@ -9803,28 +9795,28 @@
         <v>34</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F113" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H113" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I113" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="K113" s="48" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="L113" s="14">
         <v>3</v>
@@ -9837,7 +9829,7 @@
         <v>100</v>
       </c>
       <c r="O113" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P113" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9862,25 +9854,25 @@
         <v>147</v>
       </c>
       <c r="E114" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G114" s="21" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H114" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I114" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="K114" s="43" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="L114" s="21">
         <v>2</v>
@@ -9893,7 +9885,7 @@
         <v>100</v>
       </c>
       <c r="O114" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P114" s="15">
         <v>5.9999999999999995E-4</v>
@@ -9918,25 +9910,25 @@
         <v>148</v>
       </c>
       <c r="E115" s="45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F115" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G115" s="45" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H115" s="45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I115" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J115" s="45" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="K115" s="49" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="L115" s="45">
         <v>2</v>
@@ -9949,17 +9941,17 @@
         <v>100</v>
       </c>
       <c r="O115" s="61" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P115" s="15" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="Q115" s="54" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="R115" s="45"/>
       <c r="S115" s="62" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
@@ -9975,25 +9967,25 @@
         <v>149</v>
       </c>
       <c r="E116" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G116" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H116" s="21" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="I116" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="K116" s="43" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="L116" s="21">
         <v>2</v>
@@ -10006,7 +9998,7 @@
         <v>100</v>
       </c>
       <c r="O116" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P116" s="15">
         <v>1.1999999999999999E-3</v>
@@ -10031,25 +10023,25 @@
         <v>150</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F117" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H117" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I117" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="K117" s="48" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="L117" s="14">
         <v>2</v>
@@ -10062,7 +10054,7 @@
         <v>100</v>
       </c>
       <c r="O117" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P117" s="15">
         <v>1E-3</v>
@@ -10087,25 +10079,25 @@
         <v>151</v>
       </c>
       <c r="E118" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F118" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G118" s="21" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H118" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I118" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J118" s="21" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="K118" s="43" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="L118" s="21">
         <v>4</v>
@@ -10118,7 +10110,7 @@
         <v>100</v>
       </c>
       <c r="O118" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P118" s="15">
         <v>1.0200000000000001E-2</v>
@@ -10143,25 +10135,25 @@
         <v>152</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F119" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G119" s="45" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H119" s="14" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="I119" s="21" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="K119" s="48" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="L119" s="14">
         <v>2</v>
@@ -10174,7 +10166,7 @@
         <v>100</v>
       </c>
       <c r="O119" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P119" s="15">
         <v>1.1999999999999999E-3</v>
@@ -10199,25 +10191,25 @@
         <v>153</v>
       </c>
       <c r="E120" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F120" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G120" s="21" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H120" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I120" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J120" s="21" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="K120" s="50" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="L120" s="21">
         <v>8</v>
@@ -10230,7 +10222,7 @@
         <v>100</v>
       </c>
       <c r="O120" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P120" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10255,25 +10247,25 @@
         <v>154</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F121" s="47" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H121" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I121" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="K121" s="51" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="L121" s="14">
         <v>8</v>
@@ -10286,7 +10278,7 @@
         <v>100</v>
       </c>
       <c r="O121" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P121" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10311,25 +10303,25 @@
         <v>155</v>
       </c>
       <c r="E122" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F122" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G122" s="21" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H122" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I122" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J122" s="21" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="K122" s="43" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="L122" s="21">
         <v>2</v>
@@ -10342,7 +10334,7 @@
         <v>100</v>
       </c>
       <c r="O122" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P122" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10367,25 +10359,25 @@
         <v>156</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F123" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G123" s="14" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H123" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I123" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="K123" s="48" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="L123" s="14">
         <v>2</v>
@@ -10398,7 +10390,7 @@
         <v>100</v>
       </c>
       <c r="O123" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P123" s="15">
         <v>6.9999999999999999E-4</v>
@@ -10423,25 +10415,25 @@
         <v>157</v>
       </c>
       <c r="E124" s="21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G124" s="21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H124" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I124" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J124" s="21" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="K124" s="43" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="L124" s="21">
         <v>2</v>
@@ -10454,7 +10446,7 @@
         <v>100</v>
       </c>
       <c r="O124" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P124" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10479,25 +10471,25 @@
         <v>158</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F125" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G125" s="14" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H125" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I125" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="K125" s="48" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="L125" s="14">
         <v>2</v>
@@ -10510,7 +10502,7 @@
         <v>100</v>
       </c>
       <c r="O125" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P125" s="15">
         <v>5.0000000000000001E-4</v>
@@ -10535,25 +10527,25 @@
         <v>159</v>
       </c>
       <c r="E126" s="45" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F126" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G126" s="45" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H126" s="45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I126" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J126" s="45" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="K126" s="49" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="L126" s="45">
         <v>2</v>
@@ -10566,17 +10558,17 @@
         <v>100</v>
       </c>
       <c r="O126" s="61" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P126" s="15" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="Q126" s="54" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="R126" s="45"/>
       <c r="S126" s="62" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
@@ -10592,25 +10584,25 @@
         <v>160</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F127" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G127" s="14" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H127" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I127" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="K127" s="48" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="L127" s="14">
         <v>1</v>
@@ -10623,7 +10615,7 @@
         <v>100</v>
       </c>
       <c r="O127" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P127" s="15">
         <v>1.03E-2</v>
@@ -10648,25 +10640,25 @@
         <v>161</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F128" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H128" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I128" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="K128" s="48" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="L128" s="14">
         <v>2</v>
@@ -10679,7 +10671,7 @@
         <v>100</v>
       </c>
       <c r="O128" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P128" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10704,25 +10696,25 @@
         <v>162</v>
       </c>
       <c r="E129" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G129" s="21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H129" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I129" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J129" s="21" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="K129" s="43" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="L129" s="21">
         <v>1</v>
@@ -10735,7 +10727,7 @@
         <v>100</v>
       </c>
       <c r="O129" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P129" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10760,25 +10752,25 @@
         <v>163</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F130" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H130" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I130" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="K130" s="48" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="L130" s="14">
         <v>1</v>
@@ -10791,7 +10783,7 @@
         <v>100</v>
       </c>
       <c r="O130" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P130" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10816,25 +10808,25 @@
         <v>164</v>
       </c>
       <c r="E131" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F131" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G131" s="21" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H131" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I131" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J131" s="21" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="K131" s="43" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="L131" s="21">
         <v>1</v>
@@ -10847,7 +10839,7 @@
         <v>100</v>
       </c>
       <c r="O131" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P131" s="15">
         <v>5.9999999999999995E-4</v>
@@ -10872,25 +10864,25 @@
         <v>165</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F132" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H132" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K132" s="48" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="L132" s="14">
         <v>1</v>
@@ -10903,7 +10895,7 @@
         <v>100</v>
       </c>
       <c r="O132" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P132" s="15">
         <v>2.01E-2</v>
@@ -10928,25 +10920,25 @@
         <v>166</v>
       </c>
       <c r="E133" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F133" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G133" s="21" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H133" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I133" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J133" s="21" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="K133" s="43" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="L133" s="21">
         <v>2</v>
@@ -10959,7 +10951,7 @@
         <v>20</v>
       </c>
       <c r="O133" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P133" s="15">
         <v>1.78E-2</v>
@@ -10984,25 +10976,25 @@
         <v>167</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F134" s="21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H134" s="14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I134" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="K134" s="48" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="L134" s="14">
         <v>1</v>
@@ -11015,7 +11007,7 @@
         <v>50</v>
       </c>
       <c r="O134" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P134" s="15">
         <v>8.0000000000000002E-3</v>
@@ -11040,25 +11032,25 @@
         <v>168</v>
       </c>
       <c r="E135" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F135" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G135" s="44" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H135" s="21" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="I135" s="21" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="J135" s="21" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="K135" s="43" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="L135" s="21">
         <v>2</v>
@@ -11071,7 +11063,7 @@
         <v>50</v>
       </c>
       <c r="O135" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P135" s="15">
         <v>7.4999999999999997E-3</v>
@@ -11090,31 +11082,31 @@
         <v>129</v>
       </c>
       <c r="C136" s="23" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>169</v>
       </c>
       <c r="E136" s="14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F136" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H136" s="14" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="K136" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L136" s="14">
         <v>6</v>
@@ -11127,7 +11119,7 @@
         <v>20</v>
       </c>
       <c r="O136" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P136" s="15">
         <v>0.25340000000000001</v>
@@ -11152,25 +11144,25 @@
         <v>170</v>
       </c>
       <c r="E137" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F137" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G137" s="21" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H137" s="21" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J137" s="21" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="K137" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L137" s="21">
         <v>1</v>
@@ -11183,7 +11175,7 @@
         <v>5</v>
       </c>
       <c r="O137" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P137" s="15">
         <v>0.25340000000000001</v>
@@ -11208,25 +11200,25 @@
         <v>171</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="F138" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="H138" s="14" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="K138" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L138" s="14">
         <v>1</v>
@@ -11239,7 +11231,7 @@
         <v>4</v>
       </c>
       <c r="O138" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P138" s="15">
         <v>0.41949999999999998</v>
@@ -11264,25 +11256,25 @@
         <v>172</v>
       </c>
       <c r="E139" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F139" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G139" s="21" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H139" s="21" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J139" s="21" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="K139" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L139" s="21">
         <v>2</v>
@@ -11295,7 +11287,7 @@
         <v>10</v>
       </c>
       <c r="O139" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P139" s="15">
         <v>6.5100000000000005E-2</v>
@@ -11320,25 +11312,25 @@
         <v>173</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F140" s="21" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H140" s="14" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="K140" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L140" s="14">
         <v>1</v>
@@ -11351,7 +11343,7 @@
         <v>4</v>
       </c>
       <c r="O140" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P140" s="15">
         <v>0.70530000000000004</v>
@@ -11376,25 +11368,25 @@
         <v>174</v>
       </c>
       <c r="E141" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F141" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G141" s="21" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H141" s="21" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J141" s="21" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="K141" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L141" s="21">
         <v>4</v>
@@ -11407,7 +11399,7 @@
         <v>15</v>
       </c>
       <c r="O141" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P141" s="15">
         <v>9.3799999999999994E-2</v>
@@ -11432,25 +11424,25 @@
         <v>175</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F142" s="21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H142" s="14" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J142" s="14" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="K142" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L142" s="14">
         <v>1</v>
@@ -11463,7 +11455,7 @@
         <v>4</v>
       </c>
       <c r="O142" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P142" s="15">
         <v>1.325</v>
@@ -11488,25 +11480,25 @@
         <v>176</v>
       </c>
       <c r="E143" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F143" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G143" s="21" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H143" s="21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J143" s="21" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="K143" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L143" s="21">
         <v>1</v>
@@ -11519,7 +11511,7 @@
         <v>4</v>
       </c>
       <c r="O143" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P143" s="15">
         <v>1.2709999999999999</v>
@@ -11544,25 +11536,25 @@
         <v>177</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F144" s="21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H144" s="14" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J144" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="K144" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L144" s="14">
         <v>1</v>
@@ -11575,7 +11567,7 @@
         <v>4</v>
       </c>
       <c r="O144" s="53" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="P144" s="15">
         <v>2.64</v>
@@ -11600,25 +11592,25 @@
         <v>178</v>
       </c>
       <c r="E145" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F145" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G145" s="21" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H145" s="21" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J145" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="K145" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L145" s="21">
         <v>1</v>
@@ -11631,7 +11623,7 @@
         <v>4</v>
       </c>
       <c r="O145" s="53" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="P145" s="15">
         <v>2.91</v>
@@ -11656,25 +11648,25 @@
         <v>179</v>
       </c>
       <c r="E146" s="14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F146" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G146" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H146" s="14" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="I146" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="K146" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L146" s="14">
         <v>1</v>
@@ -11687,7 +11679,7 @@
         <v>4</v>
       </c>
       <c r="O146" s="53" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="P146" s="15">
         <v>9.9945000000000004</v>
@@ -11712,25 +11704,25 @@
         <v>180</v>
       </c>
       <c r="E147" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F147" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G147" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H147" s="21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I147" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J147" s="21" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="K147" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L147" s="21">
         <v>1</v>
@@ -11743,7 +11735,7 @@
         <v>4</v>
       </c>
       <c r="O147" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P147" s="15">
         <v>0.47289999999999999</v>
@@ -11768,25 +11760,25 @@
         <v>181</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F148" s="21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G148" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H148" s="14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I148" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J148" s="14" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="K148" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L148" s="14">
         <v>2</v>
@@ -11799,7 +11791,7 @@
         <v>10</v>
       </c>
       <c r="O148" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P148" s="15">
         <v>2.3199999999999998E-2</v>
@@ -11824,25 +11816,25 @@
         <v>182</v>
       </c>
       <c r="E149" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F149" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G149" s="21" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H149" s="21" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I149" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J149" s="21" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="K149" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L149" s="21">
         <v>1</v>
@@ -11855,7 +11847,7 @@
         <v>4</v>
       </c>
       <c r="O149" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P149" s="15">
         <v>8.3531999999999993</v>
@@ -11880,25 +11872,25 @@
         <v>183</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F150" s="21" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G150" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H150" s="14" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I150" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J150" s="14" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="K150" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L150" s="14">
         <v>1</v>
@@ -11911,7 +11903,7 @@
         <v>4</v>
       </c>
       <c r="O150" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P150" s="15">
         <v>0.63719999999999999</v>
@@ -11936,25 +11928,25 @@
         <v>184</v>
       </c>
       <c r="E151" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F151" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G151" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H151" s="21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J151" s="21" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="K151" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L151" s="21">
         <v>1</v>
@@ -11967,7 +11959,7 @@
         <v>5</v>
       </c>
       <c r="O151" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P151" s="15">
         <v>7.8799999999999995E-2</v>
@@ -11992,25 +11984,25 @@
         <v>185</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F152" s="21" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="G152" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H152" s="14" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I152" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J152" s="14" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="K152" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L152" s="14">
         <v>1</v>
@@ -12023,7 +12015,7 @@
         <v>4</v>
       </c>
       <c r="O152" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P152" s="15">
         <v>1.9015</v>
@@ -12048,25 +12040,25 @@
         <v>186</v>
       </c>
       <c r="E153" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F153" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G153" s="21" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H153" s="21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I153" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J153" s="21" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="K153" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L153" s="21">
         <v>1</v>
@@ -12079,7 +12071,7 @@
         <v>5</v>
       </c>
       <c r="O153" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P153" s="22">
         <v>0.2155</v>
@@ -12104,25 +12096,25 @@
         <v>187</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F154" s="21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G154" s="14" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H154" s="14" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="I154" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J154" s="14" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="K154" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L154" s="14">
         <v>2</v>
@@ -12135,7 +12127,7 @@
         <v>7</v>
       </c>
       <c r="O154" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P154" s="15">
         <v>0.99080000000000001</v>
@@ -12160,25 +12152,25 @@
         <v>188</v>
       </c>
       <c r="E155" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F155" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G155" s="21" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H155" s="21" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I155" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J155" s="21" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="K155" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L155" s="21">
         <v>1</v>
@@ -12191,7 +12183,7 @@
         <v>4</v>
       </c>
       <c r="O155" s="53" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="P155" s="22">
         <v>0.61199999999999999</v>
@@ -12216,25 +12208,25 @@
         <v>189</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F156" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G156" s="14" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H156" s="14" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I156" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J156" s="14" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="K156" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L156" s="14">
         <v>1</v>
@@ -12247,7 +12239,7 @@
         <v>4</v>
       </c>
       <c r="O156" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P156" s="15">
         <v>1.0852999999999999</v>
@@ -12272,25 +12264,25 @@
         <v>190</v>
       </c>
       <c r="E157" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F157" s="21" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G157" s="21" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H157" s="21" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I157" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J157" s="21" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="K157" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L157" s="21">
         <v>1</v>
@@ -12303,7 +12295,7 @@
         <v>4</v>
       </c>
       <c r="O157" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P157" s="22">
         <v>0.65039999999999998</v>
@@ -12328,25 +12320,25 @@
         <v>191</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F158" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G158" s="14" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H158" s="14" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J158" s="14" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="K158" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L158" s="14">
         <v>1</v>
@@ -12359,7 +12351,7 @@
         <v>4</v>
       </c>
       <c r="O158" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P158" s="15">
         <v>1.2130000000000001</v>
@@ -12384,25 +12376,25 @@
         <v>192</v>
       </c>
       <c r="E159" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F159" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G159" s="21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H159" s="21" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I159" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J159" s="21" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="K159" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L159" s="21">
         <v>1</v>
@@ -12415,7 +12407,7 @@
         <v>5</v>
       </c>
       <c r="O159" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P159" s="22">
         <v>6.6100000000000006E-2</v>
@@ -12440,25 +12432,25 @@
         <v>193</v>
       </c>
       <c r="E160" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F160" s="14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G160" s="14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H160" s="14" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I160" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J160" s="14" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="K160" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L160" s="14">
         <v>1</v>
@@ -12471,7 +12463,7 @@
         <v>5</v>
       </c>
       <c r="O160" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P160" s="15">
         <v>7.3499999999999996E-2</v>
@@ -12496,25 +12488,25 @@
         <v>194</v>
       </c>
       <c r="E161" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F161" s="21" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G161" s="21" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H161" s="21" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="I161" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J161" s="21" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="K161" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L161" s="21">
         <v>1</v>
@@ -12527,7 +12519,7 @@
         <v>4</v>
       </c>
       <c r="O161" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P161" s="22">
         <v>0.34460000000000002</v>
@@ -12552,25 +12544,25 @@
         <v>195</v>
       </c>
       <c r="E162" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F162" s="14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G162" s="14" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H162" s="14" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I162" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J162" s="14" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="K162" s="48" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L162" s="14">
         <v>1</v>
@@ -12583,7 +12575,7 @@
         <v>4</v>
       </c>
       <c r="O162" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P162" s="15">
         <v>0.43209999999999998</v>
@@ -12608,25 +12600,25 @@
         <v>196</v>
       </c>
       <c r="E163" s="21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F163" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G163" s="21" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H163" s="21" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="I163" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J163" s="21" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="K163" s="48" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="L163" s="21">
         <v>1</v>
@@ -12639,7 +12631,7 @@
         <v>4</v>
       </c>
       <c r="O163" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P163" s="22">
         <v>0.1893</v>
@@ -12664,25 +12656,25 @@
         <v>197</v>
       </c>
       <c r="E164" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F164" s="21" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G164" s="14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H164" s="14" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="I164" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J164" s="14" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="K164" s="43" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="L164" s="14">
         <v>2</v>
@@ -12695,7 +12687,7 @@
         <v>10</v>
       </c>
       <c r="O164" s="53" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P164" s="15">
         <v>0.24660000000000001</v>
@@ -12714,31 +12706,31 @@
         <v>158</v>
       </c>
       <c r="C165" s="65" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D165" s="46" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E165" s="50" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="F165" s="47" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G165" s="50" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="H165" s="46" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I165" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J165" s="46" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="K165" s="50" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L165" s="46">
         <v>1</v>
@@ -12751,7 +12743,7 @@
         <v>4</v>
       </c>
       <c r="O165" s="66" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P165" s="67">
         <v>1.0093000000000001</v>
@@ -12770,31 +12762,31 @@
         <v>159</v>
       </c>
       <c r="C166" s="65" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D166" s="46" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E166" s="50" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F166" s="47" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="G166" s="50" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="H166" s="46" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I166" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J166" s="46" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="K166" s="50" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L166" s="46">
         <v>1</v>
@@ -12807,7 +12799,7 @@
         <v>4</v>
       </c>
       <c r="O166" s="69" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="P166" s="67">
         <v>0.42520000000000002</v>
@@ -12826,29 +12818,29 @@
         <v>160</v>
       </c>
       <c r="C167" s="23" t="s">
+        <v>809</v>
+      </c>
+      <c r="D167" s="14" t="s">
         <v>813</v>
       </c>
-      <c r="D167" s="14" t="s">
-        <v>817</v>
-      </c>
       <c r="E167" s="43" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="F167" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="G167" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="H167" s="14" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="I167" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J167" s="14"/>
       <c r="K167" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L167" s="14">
         <v>1</v>
@@ -12861,7 +12853,7 @@
         <v>3</v>
       </c>
       <c r="O167" s="53" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="P167" s="15">
         <v>9.8699999999999992</v>
@@ -12880,29 +12872,29 @@
         <v>161</v>
       </c>
       <c r="C168" s="23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E168" s="43" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="F168" s="21" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="G168" s="43" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="H168" s="14" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="I168" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J168" s="14"/>
       <c r="K168" s="43" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="L168" s="14">
         <v>1</v>
@@ -12915,7 +12907,7 @@
         <v>3</v>
       </c>
       <c r="O168" s="53" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="P168" s="15">
         <v>99</v>
@@ -12934,23 +12926,23 @@
         <v>162</v>
       </c>
       <c r="C169" s="23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E169" s="43" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="F169" s="21"/>
       <c r="G169" s="43" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="H169" s="14" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="I169" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J169" s="14"/>
       <c r="K169" s="43"/>
@@ -12965,7 +12957,7 @@
         <v>3</v>
       </c>
       <c r="O169" s="52" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="P169" s="15"/>
       <c r="Q169" s="15">
@@ -12982,23 +12974,23 @@
         <v>163</v>
       </c>
       <c r="C170" s="23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E170" s="43" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F170" s="21"/>
       <c r="G170" s="43" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H170" s="14" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I170" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J170" s="14"/>
       <c r="K170" s="43"/>
@@ -13013,7 +13005,7 @@
         <v>3</v>
       </c>
       <c r="O170" s="52" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="P170" s="15"/>
       <c r="Q170" s="15">
@@ -13030,23 +13022,23 @@
         <v>164</v>
       </c>
       <c r="C171" s="23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E171" s="43" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="F171" s="21"/>
       <c r="G171" s="43" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="H171" s="14" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="I171" s="14" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="J171" s="14"/>
       <c r="K171" s="43"/>
@@ -13061,7 +13053,7 @@
         <v>3</v>
       </c>
       <c r="O171" s="52" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="P171" s="15"/>
       <c r="Q171" s="15">
@@ -13092,7 +13084,7 @@
       <c r="P172" s="73"/>
       <c r="Q172" s="18">
         <f>SUM(Q8:Q171)</f>
-        <v>641.74730000000022</v>
+        <v>643.6573000000003</v>
       </c>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
@@ -13118,7 +13110,7 @@
       <c r="P173" s="73"/>
       <c r="Q173" s="19">
         <f>Q172/3</f>
-        <v>213.91576666666674</v>
+        <v>214.55243333333343</v>
       </c>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
@@ -13134,166 +13126,166 @@
     <mergeCell ref="S2:S6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O30" r:id="rId1"/>
-    <hyperlink ref="O39" r:id="rId2"/>
-    <hyperlink ref="O40" r:id="rId3"/>
-    <hyperlink ref="O44" r:id="rId4"/>
-    <hyperlink ref="O45" r:id="rId5"/>
-    <hyperlink ref="O46" r:id="rId6"/>
-    <hyperlink ref="O49" r:id="rId7"/>
-    <hyperlink ref="O53" r:id="rId8"/>
-    <hyperlink ref="O54" r:id="rId9"/>
-    <hyperlink ref="O56" r:id="rId10"/>
-    <hyperlink ref="O57" r:id="rId11"/>
-    <hyperlink ref="O58" r:id="rId12"/>
-    <hyperlink ref="O59" r:id="rId13"/>
-    <hyperlink ref="O60" r:id="rId14"/>
-    <hyperlink ref="O62" r:id="rId15"/>
-    <hyperlink ref="O63" r:id="rId16"/>
-    <hyperlink ref="O64" r:id="rId17"/>
-    <hyperlink ref="O67" r:id="rId18"/>
-    <hyperlink ref="O68" r:id="rId19"/>
-    <hyperlink ref="O69" r:id="rId20"/>
-    <hyperlink ref="O70" r:id="rId21"/>
-    <hyperlink ref="O71" r:id="rId22"/>
-    <hyperlink ref="O73" r:id="rId23"/>
-    <hyperlink ref="O74" r:id="rId24"/>
-    <hyperlink ref="O79" r:id="rId25"/>
-    <hyperlink ref="O80" r:id="rId26"/>
-    <hyperlink ref="O81" r:id="rId27"/>
-    <hyperlink ref="O82" r:id="rId28"/>
-    <hyperlink ref="O86" r:id="rId29"/>
-    <hyperlink ref="O88" r:id="rId30"/>
-    <hyperlink ref="O93" r:id="rId31"/>
-    <hyperlink ref="O136" r:id="rId32"/>
-    <hyperlink ref="O137" r:id="rId33"/>
-    <hyperlink ref="O141" r:id="rId34"/>
-    <hyperlink ref="O148" r:id="rId35"/>
-    <hyperlink ref="O149" r:id="rId36"/>
-    <hyperlink ref="O150" r:id="rId37"/>
-    <hyperlink ref="O151" r:id="rId38"/>
-    <hyperlink ref="O154" r:id="rId39"/>
-    <hyperlink ref="O161" r:id="rId40"/>
-    <hyperlink ref="O170" r:id="rId41"/>
-    <hyperlink ref="O169" r:id="rId42"/>
-    <hyperlink ref="O171" r:id="rId43"/>
-    <hyperlink ref="O167" r:id="rId44"/>
-    <hyperlink ref="O166" r:id="rId45"/>
-    <hyperlink ref="O8" r:id="rId46"/>
-    <hyperlink ref="O9" r:id="rId47"/>
-    <hyperlink ref="O10" r:id="rId48"/>
-    <hyperlink ref="O11" r:id="rId49"/>
-    <hyperlink ref="O13" r:id="rId50"/>
-    <hyperlink ref="O14" r:id="rId51"/>
-    <hyperlink ref="O15" r:id="rId52"/>
-    <hyperlink ref="O16" r:id="rId53"/>
-    <hyperlink ref="O17" r:id="rId54"/>
-    <hyperlink ref="O18" r:id="rId55"/>
-    <hyperlink ref="O19" r:id="rId56"/>
-    <hyperlink ref="O20" r:id="rId57"/>
-    <hyperlink ref="O21" r:id="rId58"/>
-    <hyperlink ref="O22" r:id="rId59"/>
-    <hyperlink ref="O23" r:id="rId60"/>
-    <hyperlink ref="O24" r:id="rId61"/>
-    <hyperlink ref="O25" r:id="rId62"/>
-    <hyperlink ref="O26" r:id="rId63"/>
-    <hyperlink ref="O27" r:id="rId64"/>
-    <hyperlink ref="O28" r:id="rId65"/>
-    <hyperlink ref="O29" r:id="rId66"/>
-    <hyperlink ref="O31" r:id="rId67"/>
-    <hyperlink ref="O32" r:id="rId68"/>
-    <hyperlink ref="O33" r:id="rId69"/>
-    <hyperlink ref="O34" r:id="rId70"/>
-    <hyperlink ref="O35" r:id="rId71"/>
-    <hyperlink ref="O36" r:id="rId72"/>
-    <hyperlink ref="O37" r:id="rId73"/>
-    <hyperlink ref="O38" r:id="rId74"/>
-    <hyperlink ref="O41" r:id="rId75"/>
-    <hyperlink ref="O42" r:id="rId76"/>
-    <hyperlink ref="O43" r:id="rId77"/>
-    <hyperlink ref="O47" r:id="rId78"/>
-    <hyperlink ref="O48" r:id="rId79"/>
-    <hyperlink ref="O50" r:id="rId80"/>
-    <hyperlink ref="O51" r:id="rId81"/>
-    <hyperlink ref="O52" r:id="rId82"/>
-    <hyperlink ref="O55" r:id="rId83"/>
-    <hyperlink ref="O65" r:id="rId84"/>
-    <hyperlink ref="O66" r:id="rId85"/>
-    <hyperlink ref="O72" r:id="rId86"/>
-    <hyperlink ref="O75" r:id="rId87"/>
-    <hyperlink ref="O77" r:id="rId88"/>
-    <hyperlink ref="O78" r:id="rId89"/>
-    <hyperlink ref="O87" r:id="rId90"/>
-    <hyperlink ref="O89" r:id="rId91"/>
-    <hyperlink ref="O90" r:id="rId92"/>
-    <hyperlink ref="O91" r:id="rId93"/>
-    <hyperlink ref="O92" r:id="rId94"/>
-    <hyperlink ref="O94" r:id="rId95"/>
-    <hyperlink ref="O95" r:id="rId96"/>
-    <hyperlink ref="O96" r:id="rId97"/>
-    <hyperlink ref="O97" r:id="rId98"/>
-    <hyperlink ref="O98" r:id="rId99"/>
-    <hyperlink ref="O100" r:id="rId100"/>
-    <hyperlink ref="O101" r:id="rId101"/>
-    <hyperlink ref="O102" r:id="rId102"/>
-    <hyperlink ref="O103" r:id="rId103"/>
-    <hyperlink ref="O104" r:id="rId104"/>
-    <hyperlink ref="O105" r:id="rId105"/>
-    <hyperlink ref="O106" r:id="rId106"/>
-    <hyperlink ref="O107" r:id="rId107"/>
-    <hyperlink ref="O108" r:id="rId108"/>
-    <hyperlink ref="O110" r:id="rId109"/>
-    <hyperlink ref="O111" r:id="rId110"/>
-    <hyperlink ref="O114" r:id="rId111"/>
-    <hyperlink ref="O116" r:id="rId112"/>
-    <hyperlink ref="O117" r:id="rId113"/>
-    <hyperlink ref="O118" r:id="rId114"/>
-    <hyperlink ref="O120" r:id="rId115"/>
-    <hyperlink ref="O121" r:id="rId116"/>
-    <hyperlink ref="O122" r:id="rId117"/>
-    <hyperlink ref="O123" r:id="rId118"/>
-    <hyperlink ref="O124" r:id="rId119"/>
-    <hyperlink ref="O125" r:id="rId120"/>
-    <hyperlink ref="O126" r:id="rId121"/>
-    <hyperlink ref="O127" r:id="rId122"/>
-    <hyperlink ref="O128" r:id="rId123"/>
-    <hyperlink ref="O129" r:id="rId124"/>
-    <hyperlink ref="O130" r:id="rId125"/>
-    <hyperlink ref="O131" r:id="rId126"/>
-    <hyperlink ref="O132" r:id="rId127"/>
-    <hyperlink ref="O133" r:id="rId128"/>
-    <hyperlink ref="O134" r:id="rId129"/>
-    <hyperlink ref="O138" r:id="rId130"/>
-    <hyperlink ref="O139" r:id="rId131"/>
-    <hyperlink ref="O140" r:id="rId132"/>
-    <hyperlink ref="O142" r:id="rId133"/>
-    <hyperlink ref="O143" r:id="rId134"/>
-    <hyperlink ref="O147" r:id="rId135"/>
-    <hyperlink ref="O152" r:id="rId136"/>
-    <hyperlink ref="O153" r:id="rId137"/>
-    <hyperlink ref="O156" r:id="rId138"/>
-    <hyperlink ref="O157" r:id="rId139"/>
-    <hyperlink ref="O158" r:id="rId140"/>
-    <hyperlink ref="O159" r:id="rId141"/>
-    <hyperlink ref="O160" r:id="rId142"/>
-    <hyperlink ref="O162" r:id="rId143"/>
-    <hyperlink ref="O163" r:id="rId144"/>
-    <hyperlink ref="O164" r:id="rId145"/>
-    <hyperlink ref="O12" r:id="rId146"/>
-    <hyperlink ref="O61" r:id="rId147"/>
-    <hyperlink ref="O83" r:id="rId148"/>
-    <hyperlink ref="O84" r:id="rId149"/>
-    <hyperlink ref="O85" r:id="rId150"/>
-    <hyperlink ref="O135" r:id="rId151"/>
-    <hyperlink ref="O144" r:id="rId152"/>
-    <hyperlink ref="O145" r:id="rId153"/>
-    <hyperlink ref="O146" r:id="rId154"/>
-    <hyperlink ref="O155" r:id="rId155"/>
-    <hyperlink ref="O109" r:id="rId156"/>
-    <hyperlink ref="O113" r:id="rId157"/>
-    <hyperlink ref="O165" r:id="rId158"/>
-    <hyperlink ref="O119" r:id="rId159"/>
-    <hyperlink ref="O76" r:id="rId160"/>
+    <hyperlink ref="O30" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="O40" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O45" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O46" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O49" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O53" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O54" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O56" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O57" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O58" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O59" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O60" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O62" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O63" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O64" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O67" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O68" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O69" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O70" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O71" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O73" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O74" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O79" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O80" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O81" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O82" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O86" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O88" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O93" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O136" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O137" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O141" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O148" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O149" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O150" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O151" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O154" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O161" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O170" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O169" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O171" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O167" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O166" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O8" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O9" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O10" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O11" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O13" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O14" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O15" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O16" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O17" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O18" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O19" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O20" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O21" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O22" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O23" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O24" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O25" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O26" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O27" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O29" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O31" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O32" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O33" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O34" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O35" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O36" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O37" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O38" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O41" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O42" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O43" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O47" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="O48" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="O50" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="O51" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="O52" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="O55" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="O65" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="O66" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="O72" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="O75" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="O77" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="O78" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="O87" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="O89" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="O90" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="O91" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="O92" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="O94" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="O95" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="O96" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="O97" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="O98" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="O100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="O101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="O102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="O103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="O104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="O105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="O106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="O107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="O108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="O110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="O111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="O114" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="O116" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="O117" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="O118" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="O120" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="O121" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="O122" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="O123" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="O124" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="O125" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="O126" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="O127" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="O128" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="O129" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="O130" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="O131" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="O132" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="O133" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="O134" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="O138" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="O139" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="O140" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="O142" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="O143" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="O147" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="O152" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="O153" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="O156" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="O157" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="O158" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="O159" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="O160" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="O162" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="O163" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="O164" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="O12" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="O61" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="O83" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="O84" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="O85" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="O135" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="O144" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="O145" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="O146" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="O155" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="O109" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="O113" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="O165" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="O119" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="O76" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="O28" r:id="rId160" xr:uid="{950F532B-7760-4EB0-875A-88AFAD87CA87}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId161"/>

--- a/Design-Files/Carrier-Board-v1.0/BOM/eSpark_BOM_Carrier-Board-v1.0.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/eSpark_BOM_Carrier-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="895">
   <si>
     <t>Component list</t>
   </si>
@@ -2668,6 +2668,42 @@
   </si>
   <si>
     <t>C23404</t>
+  </si>
+  <si>
+    <t>250V 10A 3 -40℃~+105℃ 1.5 1 16~28 3.5mm 1x3P Green Plug P=3.5mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>DB2EK-3.5-3P-GN-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORABO </t>
+  </si>
+  <si>
+    <t>C430549</t>
+  </si>
+  <si>
+    <t>S108510003</t>
+  </si>
+  <si>
+    <t>Ckmtw</t>
+  </si>
+  <si>
+    <t>C385814</t>
+  </si>
+  <si>
+    <t>Network cables ROHS</t>
+  </si>
+  <si>
+    <t>S108510001</t>
+  </si>
+  <si>
+    <t>C385812</t>
+  </si>
+  <si>
+    <t>S108510002</t>
+  </si>
+  <si>
+    <t>C385813</t>
   </si>
 </sst>
 </file>
@@ -3356,6 +3392,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3378,15 +3423,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3730,7 +3766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z186"/>
+  <dimension ref="A1:Z190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
@@ -3767,15 +3803,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="75"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
     </row>
@@ -3802,7 +3838,7 @@
       <c r="P2" s="33"/>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
-      <c r="S2" s="75"/>
+      <c r="S2" s="78"/>
     </row>
     <row r="3" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -3827,7 +3863,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
-      <c r="S3" s="76"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3848,7 +3884,7 @@
       <c r="P4" s="25"/>
       <c r="Q4" s="25"/>
       <c r="R4" s="25"/>
-      <c r="S4" s="76"/>
+      <c r="S4" s="79"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3869,7 +3905,7 @@
       <c r="P5" s="36"/>
       <c r="Q5" s="36"/>
       <c r="R5" s="36"/>
-      <c r="S5" s="76"/>
+      <c r="S5" s="79"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -3890,7 +3926,7 @@
       <c r="P6" s="36"/>
       <c r="Q6" s="36"/>
       <c r="R6" s="36"/>
-      <c r="S6" s="77"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -4008,7 +4044,7 @@
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B165" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B169" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -9101,7 +9137,7 @@
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="C100" s="78" t="s">
+      <c r="C100" s="71" t="s">
         <v>34</v>
       </c>
       <c r="D100" s="45" t="s">
@@ -9119,7 +9155,7 @@
       <c r="H100" s="45" t="s">
         <v>530</v>
       </c>
-      <c r="I100" s="79" t="s">
+      <c r="I100" s="72" t="s">
         <v>790</v>
       </c>
       <c r="J100" s="45" t="s">
@@ -9160,7 +9196,7 @@
         <f>ROW(B101) - ROW($B$7)</f>
         <v>94</v>
       </c>
-      <c r="C101" s="78" t="s">
+      <c r="C101" s="71" t="s">
         <v>34</v>
       </c>
       <c r="D101" s="44" t="s">
@@ -9178,10 +9214,10 @@
       <c r="H101" s="44" t="s">
         <v>530</v>
       </c>
-      <c r="I101" s="79" t="s">
-        <v>790</v>
-      </c>
-      <c r="J101" s="80" t="s">
+      <c r="I101" s="72" t="s">
+        <v>790</v>
+      </c>
+      <c r="J101" s="73" t="s">
         <v>790</v>
       </c>
       <c r="K101" s="49" t="s">
@@ -11211,7 +11247,7 @@
         <v>1</v>
       </c>
       <c r="M137" s="14">
-        <f t="shared" ref="M137:M172" si="64">L137*3</f>
+        <f t="shared" ref="M137:M176" si="64">L137*3</f>
         <v>3</v>
       </c>
       <c r="N137" s="21">
@@ -12742,206 +12778,204 @@
       <c r="R164" s="14"/>
       <c r="S164" s="20"/>
     </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" ht="48" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
-      <c r="B165" s="17">
-        <f t="shared" si="0"/>
+      <c r="B165" s="16">
+        <f>ROW(B165) - ROW($B$7)</f>
         <v>158</v>
       </c>
       <c r="C165" s="65" t="s">
         <v>792</v>
       </c>
-      <c r="D165" s="46" t="s">
-        <v>793</v>
-      </c>
-      <c r="E165" s="50" t="s">
-        <v>850</v>
-      </c>
-      <c r="F165" s="47" t="s">
+      <c r="D165" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E165" s="43" t="s">
+        <v>883</v>
+      </c>
+      <c r="F165" s="21" t="s">
         <v>812</v>
       </c>
-      <c r="G165" s="50" t="s">
-        <v>851</v>
-      </c>
-      <c r="H165" s="46" t="s">
-        <v>550</v>
+      <c r="G165" s="43" t="s">
+        <v>884</v>
+      </c>
+      <c r="H165" s="14" t="s">
+        <v>885</v>
       </c>
       <c r="I165" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="J165" s="46" t="s">
-        <v>853</v>
-      </c>
-      <c r="K165" s="50" t="s">
-        <v>790</v>
-      </c>
-      <c r="L165" s="46">
-        <v>1</v>
+      <c r="J165" s="14" t="s">
+        <v>886</v>
+      </c>
+      <c r="K165" s="43" t="s">
+        <v>790</v>
+      </c>
+      <c r="L165" s="14">
+        <v>5</v>
       </c>
       <c r="M165" s="14">
         <f t="shared" si="64"/>
-        <v>3</v>
-      </c>
-      <c r="N165" s="46">
-        <v>4</v>
-      </c>
-      <c r="O165" s="66" t="s">
-        <v>814</v>
-      </c>
-      <c r="P165" s="67">
-        <v>1.0093000000000001</v>
+        <v>15</v>
+      </c>
+      <c r="N165" s="14">
+        <v>20</v>
+      </c>
+      <c r="O165" s="53" t="s">
+        <v>814</v>
+      </c>
+      <c r="P165" s="15">
+        <v>0.28139999999999998</v>
       </c>
       <c r="Q165" s="15">
-        <f t="shared" ref="Q165:Q172" si="79">P165*N165</f>
-        <v>4.0372000000000003</v>
-      </c>
-      <c r="R165" s="46"/>
+        <f>P165*N165</f>
+        <v>5.6280000000000001</v>
+      </c>
+      <c r="R165" s="14"/>
       <c r="S165" s="20"/>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="16">
-        <f>ROW(B166) - ROW($B$7)</f>
+        <f t="shared" ref="B166:B168" si="79">ROW(B166) - ROW($B$7)</f>
         <v>159</v>
       </c>
       <c r="C166" s="65" t="s">
         <v>792</v>
       </c>
-      <c r="D166" s="46" t="s">
-        <v>794</v>
-      </c>
-      <c r="E166" s="50" t="s">
-        <v>852</v>
-      </c>
-      <c r="F166" s="47" t="s">
-        <v>790</v>
-      </c>
-      <c r="G166" s="50" t="s">
-        <v>795</v>
-      </c>
-      <c r="H166" s="46" t="s">
-        <v>550</v>
+      <c r="D166" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E166" s="43" t="s">
+        <v>890</v>
+      </c>
+      <c r="F166" s="21" t="s">
+        <v>812</v>
+      </c>
+      <c r="G166" s="43" t="s">
+        <v>887</v>
+      </c>
+      <c r="H166" s="14" t="s">
+        <v>888</v>
       </c>
       <c r="I166" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="J166" s="46" t="s">
-        <v>854</v>
-      </c>
-      <c r="K166" s="50" t="s">
-        <v>790</v>
-      </c>
-      <c r="L166" s="46">
-        <v>1</v>
+      <c r="J166" s="14" t="s">
+        <v>889</v>
+      </c>
+      <c r="K166" s="43" t="s">
+        <v>790</v>
+      </c>
+      <c r="L166" s="14">
+        <v>2</v>
       </c>
       <c r="M166" s="14">
         <f t="shared" si="64"/>
+        <v>6</v>
+      </c>
+      <c r="N166" s="14">
+        <v>10</v>
+      </c>
+      <c r="O166" s="53" t="s">
+        <v>814</v>
+      </c>
+      <c r="P166" s="15">
+        <v>0.1767</v>
+      </c>
+      <c r="Q166" s="15">
+        <f t="shared" ref="Q166:Q168" si="80">P166*N166</f>
+        <v>1.7669999999999999</v>
+      </c>
+      <c r="R166" s="14"/>
+      <c r="S166" s="20"/>
+    </row>
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A167" s="1"/>
+      <c r="B167" s="16">
+        <f t="shared" si="79"/>
+        <v>160</v>
+      </c>
+      <c r="C167" s="65" t="s">
+        <v>792</v>
+      </c>
+      <c r="D167" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E167" s="43" t="s">
+        <v>890</v>
+      </c>
+      <c r="F167" s="21" t="s">
+        <v>812</v>
+      </c>
+      <c r="G167" s="43" t="s">
+        <v>891</v>
+      </c>
+      <c r="H167" s="14" t="s">
+        <v>888</v>
+      </c>
+      <c r="I167" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="J167" s="14" t="s">
+        <v>892</v>
+      </c>
+      <c r="K167" s="43" t="s">
+        <v>790</v>
+      </c>
+      <c r="L167" s="14">
         <v>3</v>
-      </c>
-      <c r="N166" s="46">
-        <v>4</v>
-      </c>
-      <c r="O166" s="69" t="s">
-        <v>814</v>
-      </c>
-      <c r="P166" s="67">
-        <v>0.42520000000000002</v>
-      </c>
-      <c r="Q166" s="15">
-        <f t="shared" si="79"/>
-        <v>1.7008000000000001</v>
-      </c>
-      <c r="R166" s="46"/>
-      <c r="S166" s="20"/>
-    </row>
-    <row r="167" spans="1:26" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="63"/>
-      <c r="B167" s="64">
-        <f t="shared" ref="B167:B172" si="80">ROW(B167) - ROW($B$7)</f>
-        <v>160</v>
-      </c>
-      <c r="C167" s="23" t="s">
-        <v>792</v>
-      </c>
-      <c r="D167" s="14" t="s">
-        <v>796</v>
-      </c>
-      <c r="E167" s="43" t="s">
-        <v>797</v>
-      </c>
-      <c r="F167" s="21" t="s">
-        <v>790</v>
-      </c>
-      <c r="G167" s="43" t="s">
-        <v>790</v>
-      </c>
-      <c r="H167" s="14" t="s">
-        <v>798</v>
-      </c>
-      <c r="I167" s="14" t="s">
-        <v>790</v>
-      </c>
-      <c r="J167" s="14"/>
-      <c r="K167" s="43" t="s">
-        <v>790</v>
-      </c>
-      <c r="L167" s="14">
-        <v>1</v>
       </c>
       <c r="M167" s="14">
         <f t="shared" si="64"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N167" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O167" s="53" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P167" s="15">
-        <v>9.8699999999999992</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="Q167" s="15">
-        <f t="shared" si="79"/>
-        <v>29.61</v>
+        <f t="shared" si="80"/>
+        <v>0.91500000000000004</v>
       </c>
       <c r="R167" s="14"/>
       <c r="S167" s="20"/>
-      <c r="U167"/>
-      <c r="V167"/>
-      <c r="W167"/>
-      <c r="X167"/>
-      <c r="Y167"/>
-      <c r="Z167"/>
-    </row>
-    <row r="168" spans="1:26" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="63"/>
-      <c r="B168" s="64">
-        <f t="shared" si="80"/>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A168" s="1"/>
+      <c r="B168" s="16">
+        <f t="shared" si="79"/>
         <v>161</v>
       </c>
-      <c r="C168" s="23" t="s">
+      <c r="C168" s="65" t="s">
         <v>792</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="E168" s="43" t="s">
-        <v>800</v>
+        <v>890</v>
       </c>
       <c r="F168" s="21" t="s">
-        <v>790</v>
+        <v>812</v>
       </c>
       <c r="G168" s="43" t="s">
-        <v>801</v>
+        <v>893</v>
       </c>
       <c r="H168" s="14" t="s">
-        <v>802</v>
+        <v>888</v>
       </c>
       <c r="I168" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="J168" s="14"/>
+      <c r="J168" s="14" t="s">
+        <v>894</v>
+      </c>
       <c r="K168" s="43" t="s">
         <v>790</v>
       </c>
@@ -12953,210 +12987,224 @@
         <v>3</v>
       </c>
       <c r="N168" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O168" s="53" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="P168" s="15">
-        <v>99</v>
+        <v>0.1381</v>
       </c>
       <c r="Q168" s="15">
-        <f t="shared" si="79"/>
-        <v>297</v>
+        <f t="shared" si="80"/>
+        <v>0.6905</v>
       </c>
       <c r="R168" s="14"/>
       <c r="S168" s="20"/>
-      <c r="U168"/>
-      <c r="V168"/>
-      <c r="W168"/>
-      <c r="X168"/>
-      <c r="Y168"/>
-      <c r="Z168"/>
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
-      <c r="B169" s="16">
-        <f t="shared" si="80"/>
+      <c r="B169" s="17">
+        <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="C169" s="23" t="s">
+      <c r="C169" s="65" t="s">
         <v>792</v>
       </c>
-      <c r="D169" s="14" t="s">
-        <v>790</v>
-      </c>
-      <c r="E169" s="43" t="s">
-        <v>803</v>
-      </c>
-      <c r="F169" s="21"/>
-      <c r="G169" s="43" t="s">
-        <v>804</v>
-      </c>
-      <c r="H169" s="14" t="s">
-        <v>805</v>
+      <c r="D169" s="46" t="s">
+        <v>793</v>
+      </c>
+      <c r="E169" s="50" t="s">
+        <v>850</v>
+      </c>
+      <c r="F169" s="47" t="s">
+        <v>812</v>
+      </c>
+      <c r="G169" s="50" t="s">
+        <v>851</v>
+      </c>
+      <c r="H169" s="46" t="s">
+        <v>550</v>
       </c>
       <c r="I169" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="J169" s="14"/>
-      <c r="K169" s="43"/>
-      <c r="L169" s="14">
+      <c r="J169" s="46" t="s">
+        <v>853</v>
+      </c>
+      <c r="K169" s="50" t="s">
+        <v>790</v>
+      </c>
+      <c r="L169" s="46">
         <v>1</v>
       </c>
       <c r="M169" s="14">
         <f t="shared" si="64"/>
         <v>3</v>
       </c>
-      <c r="N169" s="14">
-        <v>3</v>
-      </c>
-      <c r="O169" s="52" t="s">
-        <v>805</v>
-      </c>
-      <c r="P169" s="15"/>
+      <c r="N169" s="46">
+        <v>4</v>
+      </c>
+      <c r="O169" s="66" t="s">
+        <v>814</v>
+      </c>
+      <c r="P169" s="67">
+        <v>1.0093000000000001</v>
+      </c>
       <c r="Q169" s="15">
-        <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="R169" s="14"/>
+        <f t="shared" ref="Q169:Q176" si="81">P169*N169</f>
+        <v>4.0372000000000003</v>
+      </c>
+      <c r="R169" s="46"/>
       <c r="S169" s="20"/>
     </row>
-    <row r="170" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="16">
-        <f t="shared" si="80"/>
+        <f>ROW(B170) - ROW($B$7)</f>
         <v>163</v>
       </c>
-      <c r="C170" s="23" t="s">
+      <c r="C170" s="65" t="s">
         <v>792</v>
       </c>
-      <c r="D170" s="14" t="s">
-        <v>790</v>
-      </c>
-      <c r="E170" s="43" t="s">
-        <v>806</v>
-      </c>
-      <c r="F170" s="21" t="s">
-        <v>790</v>
-      </c>
-      <c r="G170" s="43" t="s">
-        <v>807</v>
-      </c>
-      <c r="H170" s="14" t="s">
-        <v>808</v>
+      <c r="D170" s="46" t="s">
+        <v>794</v>
+      </c>
+      <c r="E170" s="50" t="s">
+        <v>852</v>
+      </c>
+      <c r="F170" s="47" t="s">
+        <v>790</v>
+      </c>
+      <c r="G170" s="50" t="s">
+        <v>795</v>
+      </c>
+      <c r="H170" s="46" t="s">
+        <v>550</v>
       </c>
       <c r="I170" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="J170" s="14"/>
-      <c r="K170" s="43"/>
-      <c r="L170" s="14">
+      <c r="J170" s="46" t="s">
+        <v>854</v>
+      </c>
+      <c r="K170" s="50" t="s">
+        <v>790</v>
+      </c>
+      <c r="L170" s="46">
         <v>1</v>
       </c>
       <c r="M170" s="14">
         <f t="shared" si="64"/>
         <v>3</v>
       </c>
-      <c r="N170" s="14">
-        <v>3</v>
-      </c>
-      <c r="O170" s="52" t="s">
-        <v>808</v>
-      </c>
-      <c r="P170" s="15"/>
+      <c r="N170" s="46">
+        <v>4</v>
+      </c>
+      <c r="O170" s="69" t="s">
+        <v>814</v>
+      </c>
+      <c r="P170" s="67">
+        <v>0.42520000000000002</v>
+      </c>
       <c r="Q170" s="15">
-        <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="R170" s="14"/>
+        <f t="shared" si="81"/>
+        <v>1.7008000000000001</v>
+      </c>
+      <c r="R170" s="46"/>
       <c r="S170" s="20"/>
     </row>
-    <row r="171" spans="1:26" ht="48" x14ac:dyDescent="0.25">
-      <c r="A171" s="1"/>
-      <c r="B171" s="16">
-        <f t="shared" si="80"/>
+    <row r="171" spans="1:26" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="63"/>
+      <c r="B171" s="64">
+        <f t="shared" ref="B171:B176" si="82">ROW(B171) - ROW($B$7)</f>
         <v>164</v>
       </c>
       <c r="C171" s="23" t="s">
         <v>792</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="E171" s="43" t="s">
-        <v>861</v>
+        <v>797</v>
       </c>
       <c r="F171" s="21" t="s">
         <v>790</v>
       </c>
       <c r="G171" s="43" t="s">
-        <v>862</v>
+        <v>790</v>
       </c>
       <c r="H171" s="14" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="I171" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="J171" s="14" t="s">
-        <v>790</v>
-      </c>
+      <c r="J171" s="14"/>
       <c r="K171" s="43" t="s">
         <v>790</v>
       </c>
       <c r="L171" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M171" s="14">
         <f t="shared" si="64"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N171" s="14">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="O171" s="53" t="s">
         <v>815</v>
       </c>
       <c r="P171" s="15">
-        <v>2.3199999999999998</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="Q171" s="15">
-        <f t="shared" si="79"/>
-        <v>231.99999999999997</v>
+        <f t="shared" si="81"/>
+        <v>29.61</v>
       </c>
       <c r="R171" s="14"/>
       <c r="S171" s="20"/>
-    </row>
-    <row r="172" spans="1:26" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="1"/>
-      <c r="B172" s="16">
-        <f t="shared" si="80"/>
+      <c r="U171"/>
+      <c r="V171"/>
+      <c r="W171"/>
+      <c r="X171"/>
+      <c r="Y171"/>
+      <c r="Z171"/>
+    </row>
+    <row r="172" spans="1:26" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="63"/>
+      <c r="B172" s="64">
+        <f t="shared" si="82"/>
         <v>165</v>
       </c>
       <c r="C172" s="23" t="s">
         <v>792</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="E172" s="43" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="F172" s="21" t="s">
         <v>790</v>
       </c>
       <c r="G172" s="43" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="H172" s="14" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="I172" s="14" t="s">
         <v>790</v>
       </c>
       <c r="J172" s="14"/>
-      <c r="K172" s="43"/>
+      <c r="K172" s="43" t="s">
+        <v>790</v>
+      </c>
       <c r="L172" s="14">
         <v>1</v>
       </c>
@@ -13167,83 +13215,295 @@
       <c r="N172" s="14">
         <v>3</v>
       </c>
-      <c r="O172" s="52" t="s">
-        <v>817</v>
-      </c>
-      <c r="P172" s="15"/>
+      <c r="O172" s="53" t="s">
+        <v>816</v>
+      </c>
+      <c r="P172" s="15">
+        <v>99</v>
+      </c>
       <c r="Q172" s="15">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="81"/>
+        <v>297</v>
       </c>
       <c r="R172" s="14"/>
       <c r="S172" s="20"/>
-    </row>
-    <row r="173" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U172"/>
+      <c r="V172"/>
+      <c r="W172"/>
+      <c r="X172"/>
+      <c r="Y172"/>
+      <c r="Z172"/>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
-      <c r="E173" s="1"/>
-      <c r="F173" s="1"/>
-      <c r="G173" s="1"/>
-      <c r="H173" s="1"/>
-      <c r="I173" s="1"/>
-      <c r="J173" s="1"/>
-      <c r="K173" s="1"/>
-      <c r="L173" s="1"/>
-      <c r="M173" s="1"/>
-      <c r="N173" s="73" t="s">
+      <c r="B173" s="16">
+        <f t="shared" si="82"/>
+        <v>166</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="D173" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E173" s="43" t="s">
+        <v>803</v>
+      </c>
+      <c r="F173" s="21"/>
+      <c r="G173" s="43" t="s">
+        <v>804</v>
+      </c>
+      <c r="H173" s="14" t="s">
+        <v>805</v>
+      </c>
+      <c r="I173" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="J173" s="14"/>
+      <c r="K173" s="43"/>
+      <c r="L173" s="14">
+        <v>1</v>
+      </c>
+      <c r="M173" s="14">
+        <f t="shared" si="64"/>
         <v>3</v>
       </c>
-      <c r="O173" s="74"/>
-      <c r="P173" s="74"/>
-      <c r="Q173" s="18">
-        <f>SUM(Q8:Q172)</f>
-        <v>880.01450000000023</v>
-      </c>
-      <c r="R173" s="1"/>
-      <c r="S173" s="1"/>
-    </row>
-    <row r="174" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N173" s="14">
+        <v>3</v>
+      </c>
+      <c r="O173" s="52" t="s">
+        <v>805</v>
+      </c>
+      <c r="P173" s="15"/>
+      <c r="Q173" s="15">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="R173" s="14"/>
+      <c r="S173" s="20"/>
+    </row>
+    <row r="174" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
-      <c r="E174" s="1"/>
-      <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
-      <c r="H174" s="1"/>
-      <c r="I174" s="1"/>
-      <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
-      <c r="L174" s="1"/>
-      <c r="M174" s="1"/>
-      <c r="N174" s="73" t="s">
+      <c r="B174" s="16">
+        <f t="shared" si="82"/>
+        <v>167</v>
+      </c>
+      <c r="C174" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="D174" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E174" s="43" t="s">
+        <v>806</v>
+      </c>
+      <c r="F174" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="G174" s="43" t="s">
+        <v>807</v>
+      </c>
+      <c r="H174" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="I174" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="J174" s="14"/>
+      <c r="K174" s="43"/>
+      <c r="L174" s="14">
+        <v>1</v>
+      </c>
+      <c r="M174" s="14">
+        <f t="shared" si="64"/>
+        <v>3</v>
+      </c>
+      <c r="N174" s="14">
+        <v>3</v>
+      </c>
+      <c r="O174" s="52" t="s">
+        <v>808</v>
+      </c>
+      <c r="P174" s="15"/>
+      <c r="Q174" s="15">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="R174" s="14"/>
+      <c r="S174" s="20"/>
+    </row>
+    <row r="175" spans="1:26" ht="48" x14ac:dyDescent="0.25">
+      <c r="A175" s="1"/>
+      <c r="B175" s="16">
+        <f t="shared" si="82"/>
+        <v>168</v>
+      </c>
+      <c r="C175" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="D175" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E175" s="43" t="s">
+        <v>861</v>
+      </c>
+      <c r="F175" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="G175" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="H175" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="I175" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="J175" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="K175" s="43" t="s">
+        <v>790</v>
+      </c>
+      <c r="L175" s="14">
         <v>4</v>
       </c>
-      <c r="O174" s="74"/>
-      <c r="P174" s="74"/>
-      <c r="Q174" s="19">
-        <f>Q173/3</f>
-        <v>293.33816666666672</v>
-      </c>
-      <c r="R174" s="1"/>
-      <c r="S174" s="1"/>
-    </row>
-    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A175" s="1"/>
-    </row>
-    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M175" s="14">
+        <f t="shared" si="64"/>
+        <v>12</v>
+      </c>
+      <c r="N175" s="14">
+        <v>100</v>
+      </c>
+      <c r="O175" s="53" t="s">
+        <v>815</v>
+      </c>
+      <c r="P175" s="15">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="Q175" s="15">
+        <f t="shared" si="81"/>
+        <v>231.99999999999997</v>
+      </c>
+      <c r="R175" s="14"/>
+      <c r="S175" s="20"/>
+    </row>
+    <row r="176" spans="1:26" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
-    </row>
-    <row r="186" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M186" s="39"/>
+      <c r="B176" s="16">
+        <f t="shared" si="82"/>
+        <v>169</v>
+      </c>
+      <c r="C176" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="E176" s="43" t="s">
+        <v>809</v>
+      </c>
+      <c r="F176" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="G176" s="43" t="s">
+        <v>810</v>
+      </c>
+      <c r="H176" s="14" t="s">
+        <v>811</v>
+      </c>
+      <c r="I176" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="J176" s="14"/>
+      <c r="K176" s="43"/>
+      <c r="L176" s="14">
+        <v>1</v>
+      </c>
+      <c r="M176" s="14">
+        <f t="shared" si="64"/>
+        <v>3</v>
+      </c>
+      <c r="N176" s="14">
+        <v>3</v>
+      </c>
+      <c r="O176" s="52" t="s">
+        <v>817</v>
+      </c>
+      <c r="P176" s="15"/>
+      <c r="Q176" s="15">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="R176" s="14"/>
+      <c r="S176" s="20"/>
+    </row>
+    <row r="177" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="K177" s="1"/>
+      <c r="L177" s="1"/>
+      <c r="M177" s="1"/>
+      <c r="N177" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="O177" s="77"/>
+      <c r="P177" s="77"/>
+      <c r="Q177" s="18">
+        <f>SUM(Q8:Q176)</f>
+        <v>889.01500000000033</v>
+      </c>
+      <c r="R177" s="1"/>
+      <c r="S177" s="1"/>
+    </row>
+    <row r="178" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+      <c r="L178" s="1"/>
+      <c r="M178" s="1"/>
+      <c r="N178" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="O178" s="77"/>
+      <c r="P178" s="77"/>
+      <c r="Q178" s="19">
+        <f>Q177/3</f>
+        <v>296.33833333333342</v>
+      </c>
+      <c r="R178" s="1"/>
+      <c r="S178" s="1"/>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A179" s="1"/>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A180" s="1"/>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M190" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="K1:S1"/>
-    <mergeCell ref="N173:P173"/>
-    <mergeCell ref="N174:P174"/>
+    <mergeCell ref="N177:P177"/>
+    <mergeCell ref="N178:P178"/>
     <mergeCell ref="S2:S6"/>
   </mergeCells>
   <hyperlinks>
@@ -13285,11 +13545,11 @@
     <hyperlink ref="O151" r:id="rId36"/>
     <hyperlink ref="O154" r:id="rId37"/>
     <hyperlink ref="O161" r:id="rId38"/>
-    <hyperlink ref="O170" r:id="rId39"/>
-    <hyperlink ref="O169" r:id="rId40"/>
-    <hyperlink ref="O172" r:id="rId41"/>
-    <hyperlink ref="O167" r:id="rId42"/>
-    <hyperlink ref="O166" r:id="rId43"/>
+    <hyperlink ref="O174" r:id="rId39"/>
+    <hyperlink ref="O173" r:id="rId40"/>
+    <hyperlink ref="O176" r:id="rId41"/>
+    <hyperlink ref="O171" r:id="rId42"/>
+    <hyperlink ref="O170" r:id="rId43"/>
     <hyperlink ref="O8" r:id="rId44"/>
     <hyperlink ref="O9" r:id="rId45"/>
     <hyperlink ref="O10" r:id="rId46"/>
@@ -13399,17 +13659,21 @@
     <hyperlink ref="O155" r:id="rId150"/>
     <hyperlink ref="O109" r:id="rId151"/>
     <hyperlink ref="O113" r:id="rId152"/>
-    <hyperlink ref="O165" r:id="rId153"/>
+    <hyperlink ref="O169" r:id="rId153"/>
     <hyperlink ref="O119" r:id="rId154"/>
     <hyperlink ref="O76" r:id="rId155"/>
     <hyperlink ref="O28" r:id="rId156"/>
-    <hyperlink ref="O171" r:id="rId157"/>
+    <hyperlink ref="O175" r:id="rId157"/>
     <hyperlink ref="O38" r:id="rId158"/>
     <hyperlink ref="O56" r:id="rId159"/>
     <hyperlink ref="O137" r:id="rId160"/>
+    <hyperlink ref="O165" r:id="rId161"/>
+    <hyperlink ref="O166" r:id="rId162"/>
+    <hyperlink ref="O167" r:id="rId163"/>
+    <hyperlink ref="O168" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId161"/>
-  <drawing r:id="rId162"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId165"/>
+  <drawing r:id="rId166"/>
 </worksheet>
 </file>